--- a/public/payslip-template.xlsx
+++ b/public/payslip-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bin\JOB\THUCTAP\NHT\Payslip\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bin\JOB\THUCTAP\NHT\Payslip\Mẫu nhập\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9364C747-8500-480F-962E-E5C7CF7F68CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C355FC4-E1C2-455D-95D4-DAE810B9D926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{E78F4DFD-1167-45B0-99FC-E4DD07682841}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{E78F4DFD-1167-45B0-99FC-E4DD07682841}"/>
   </bookViews>
   <sheets>
     <sheet name="GV" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="120">
   <si>
     <t>Đơn vị:</t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>Phụ cấp cơm</t>
+  </si>
+  <si>
+    <t>Lương tháng 13</t>
   </si>
 </sst>
 </file>
@@ -1476,45 +1479,69 @@
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1530,17 +1557,131 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1564,15 +1705,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1596,68 +1728,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1680,86 +1758,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2533,92 +2536,92 @@
       <c r="H5" s="20"/>
     </row>
     <row r="6" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="174" t="s">
+      <c r="A6" s="161" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="174"/>
-      <c r="E6" s="174"/>
-      <c r="F6" s="174"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="174"/>
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="172"/>
-      <c r="C7" s="172"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
       <c r="D7" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="162"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="172"/>
-      <c r="C8" s="172"/>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
       <c r="D8" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="172" t="s">
+      <c r="E8" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="172"/>
-      <c r="G8" s="172"/>
-      <c r="H8" s="172"/>
+      <c r="F8" s="159"/>
+      <c r="G8" s="159"/>
+      <c r="H8" s="159"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="172" t="s">
+      <c r="B9" s="159" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="172"/>
+      <c r="C9" s="159"/>
       <c r="D9" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="172" t="s">
+      <c r="E9" s="159" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="172"/>
-      <c r="G9" s="172"/>
-      <c r="H9" s="172"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="159"/>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="172"/>
-      <c r="C10" s="172"/>
+      <c r="B10" s="159"/>
+      <c r="C10" s="159"/>
       <c r="D10" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="172"/>
-      <c r="F10" s="172"/>
-      <c r="G10" s="172"/>
-      <c r="H10" s="172"/>
+      <c r="E10" s="159"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="159"/>
+      <c r="H10" s="159"/>
     </row>
     <row r="11" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="23">
         <v>1</v>
       </c>
-      <c r="B11" s="173" t="s">
+      <c r="B11" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="173"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="173"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="173"/>
-      <c r="H11" s="173"/>
+      <c r="C11" s="160"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
@@ -2885,12 +2888,12 @@
     </row>
     <row r="31" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="43"/>
-      <c r="B31" s="155" t="s">
+      <c r="B31" s="179" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="155"/>
-      <c r="D31" s="155"/>
-      <c r="E31" s="155"/>
+      <c r="C31" s="179"/>
+      <c r="D31" s="179"/>
+      <c r="E31" s="179"/>
       <c r="F31" s="13">
         <f>SUM(F21:F30)</f>
         <v>0</v>
@@ -2999,12 +3002,12 @@
     </row>
     <row r="39" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A39" s="43"/>
-      <c r="B39" s="156" t="s">
+      <c r="B39" s="180" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="157"/>
-      <c r="D39" s="157"/>
-      <c r="E39" s="157"/>
+      <c r="C39" s="181"/>
+      <c r="D39" s="181"/>
+      <c r="E39" s="181"/>
       <c r="F39" s="16">
         <f>SUM(F37:F38)</f>
         <v>0</v>
@@ -3082,13 +3085,13 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="156" t="s">
+      <c r="A44" s="180" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="157"/>
-      <c r="C44" s="157"/>
-      <c r="D44" s="157"/>
-      <c r="E44" s="158"/>
+      <c r="B44" s="181"/>
+      <c r="C44" s="181"/>
+      <c r="D44" s="181"/>
+      <c r="E44" s="182"/>
       <c r="F44" s="16">
         <f>SUM(F42:F43)</f>
         <v>0</v>
@@ -3166,13 +3169,13 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="156" t="s">
+      <c r="A49" s="180" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="157"/>
-      <c r="C49" s="157"/>
-      <c r="D49" s="157"/>
-      <c r="E49" s="158"/>
+      <c r="B49" s="181"/>
+      <c r="C49" s="181"/>
+      <c r="D49" s="181"/>
+      <c r="E49" s="182"/>
       <c r="F49" s="16">
         <f>SUM(F47:F48)</f>
         <v>0</v>
@@ -3210,23 +3213,23 @@
       <c r="D51" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="155" t="s">
+      <c r="E51" s="179" t="s">
         <v>20</v>
       </c>
-      <c r="F51" s="155"/>
-      <c r="G51" s="155"/>
+      <c r="F51" s="179"/>
+      <c r="G51" s="179"/>
       <c r="H51" s="50"/>
     </row>
     <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="159" t="s">
+      <c r="A52" s="172" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="160"/>
-      <c r="C52" s="160"/>
-      <c r="D52" s="160"/>
-      <c r="E52" s="160"/>
-      <c r="F52" s="160"/>
-      <c r="G52" s="161"/>
+      <c r="B52" s="173"/>
+      <c r="C52" s="173"/>
+      <c r="D52" s="173"/>
+      <c r="E52" s="173"/>
+      <c r="F52" s="173"/>
+      <c r="G52" s="174"/>
       <c r="H52" s="59">
         <v>0</v>
       </c>
@@ -3235,10 +3238,10 @@
       <c r="A53" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="162" t="s">
+      <c r="B53" s="175" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="162"/>
+      <c r="C53" s="175"/>
       <c r="D53" s="51"/>
       <c r="E53" s="52"/>
       <c r="F53" s="52"/>
@@ -3246,61 +3249,61 @@
       <c r="H53" s="53"/>
     </row>
     <row r="54" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="176" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="145"/>
-      <c r="C54" s="145"/>
-      <c r="D54" s="145"/>
-      <c r="E54" s="146"/>
-      <c r="F54" s="138">
-        <v>0</v>
-      </c>
-      <c r="G54" s="139"/>
-      <c r="H54" s="140"/>
+      <c r="B54" s="177"/>
+      <c r="C54" s="177"/>
+      <c r="D54" s="177"/>
+      <c r="E54" s="178"/>
+      <c r="F54" s="184">
+        <v>0</v>
+      </c>
+      <c r="G54" s="185"/>
+      <c r="H54" s="186"/>
     </row>
     <row r="55" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="176" t="s">
         <v>71</v>
       </c>
-      <c r="B55" s="145"/>
-      <c r="C55" s="145"/>
-      <c r="D55" s="145"/>
-      <c r="E55" s="146"/>
-      <c r="F55" s="138">
-        <v>0</v>
-      </c>
-      <c r="G55" s="139"/>
-      <c r="H55" s="140"/>
+      <c r="B55" s="177"/>
+      <c r="C55" s="177"/>
+      <c r="D55" s="177"/>
+      <c r="E55" s="178"/>
+      <c r="F55" s="184">
+        <v>0</v>
+      </c>
+      <c r="G55" s="185"/>
+      <c r="H55" s="186"/>
     </row>
     <row r="56" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="176" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="145"/>
-      <c r="C56" s="145"/>
-      <c r="D56" s="145"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="138">
-        <v>0</v>
-      </c>
-      <c r="G56" s="139"/>
-      <c r="H56" s="140"/>
+      <c r="B56" s="177"/>
+      <c r="C56" s="177"/>
+      <c r="D56" s="177"/>
+      <c r="E56" s="178"/>
+      <c r="F56" s="184">
+        <v>0</v>
+      </c>
+      <c r="G56" s="185"/>
+      <c r="H56" s="186"/>
     </row>
     <row r="57" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="155" t="s">
+      <c r="A57" s="179" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="155"/>
-      <c r="C57" s="155"/>
-      <c r="D57" s="155"/>
-      <c r="E57" s="155"/>
-      <c r="F57" s="141">
+      <c r="B57" s="179"/>
+      <c r="C57" s="179"/>
+      <c r="D57" s="179"/>
+      <c r="E57" s="179"/>
+      <c r="F57" s="187">
         <f>F54+F55*F56</f>
         <v>0</v>
       </c>
-      <c r="G57" s="142"/>
-      <c r="H57" s="143"/>
+      <c r="G57" s="188"/>
+      <c r="H57" s="189"/>
     </row>
     <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A58" s="54"/>
@@ -3316,36 +3319,36 @@
       <c r="A59" s="55">
         <v>3</v>
       </c>
-      <c r="B59" s="153" t="s">
+      <c r="B59" s="196" t="s">
         <v>68</v>
       </c>
-      <c r="C59" s="154"/>
-      <c r="D59" s="147"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="149"/>
+      <c r="C59" s="197"/>
+      <c r="D59" s="190"/>
+      <c r="E59" s="191"/>
+      <c r="F59" s="191"/>
+      <c r="G59" s="191"/>
+      <c r="H59" s="192"/>
     </row>
     <row r="60" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="147" t="s">
+      <c r="A60" s="190" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="148"/>
-      <c r="C60" s="149"/>
-      <c r="D60" s="150"/>
-      <c r="E60" s="151"/>
-      <c r="F60" s="151"/>
-      <c r="G60" s="151"/>
-      <c r="H60" s="152"/>
+      <c r="B60" s="191"/>
+      <c r="C60" s="192"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="194"/>
+      <c r="F60" s="194"/>
+      <c r="G60" s="194"/>
+      <c r="H60" s="195"/>
     </row>
     <row r="61" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A61" s="56">
         <v>4</v>
       </c>
-      <c r="B61" s="137" t="s">
+      <c r="B61" s="183" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="137"/>
+      <c r="C61" s="183"/>
       <c r="D61" s="57"/>
       <c r="E61" s="57"/>
       <c r="F61" s="57"/>
@@ -3357,6 +3360,36 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="E10:H10"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="B7:C7"/>
@@ -3367,36 +3400,6 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="B59:C59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3465,20 +3468,20 @@
       <c r="E5" s="82"/>
     </row>
     <row r="6" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="115" t="s">
+      <c r="A6" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="135"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="128"/>
-      <c r="C7" s="129"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="137"/>
       <c r="D7" s="86" t="s">
         <v>73</v>
       </c>
@@ -3491,12 +3494,12 @@
       <c r="A8" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="130" t="s">
+      <c r="B8" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="131"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="132"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="140"/>
       <c r="F8" s="88"/>
       <c r="G8" s="88"/>
       <c r="H8" s="88"/>
@@ -3512,36 +3515,36 @@
       <c r="H9" s="88"/>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="116" t="s">
+      <c r="A10" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="117"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="117"/>
       <c r="E10" s="91"/>
       <c r="F10" s="88"/>
       <c r="G10" s="88"/>
       <c r="H10" s="88"/>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="116" t="s">
+      <c r="A11" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="117"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="118"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="117"/>
       <c r="E11" s="91"/>
       <c r="F11" s="88"/>
       <c r="G11" s="88"/>
       <c r="H11" s="88"/>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="116" t="s">
+      <c r="A12" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="117"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="118"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="117"/>
       <c r="E12" s="92" t="e">
         <f>DAY(EOMONTH(DATE(E7,B7,1),0))</f>
         <v>#NUM!</v>
@@ -3551,134 +3554,134 @@
       <c r="H12" s="88"/>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="116" t="s">
+      <c r="A13" s="115" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="117"/>
       <c r="E13" s="91"/>
       <c r="F13" s="88"/>
       <c r="G13" s="88"/>
       <c r="H13" s="88"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="116" t="s">
+      <c r="A14" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="118"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="117"/>
       <c r="E14" s="91"/>
       <c r="F14" s="88"/>
       <c r="G14" s="88"/>
       <c r="H14" s="88"/>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="116" t="s">
+      <c r="A15" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="117"/>
       <c r="E15" s="91"/>
       <c r="F15" s="88"/>
       <c r="G15" s="88"/>
       <c r="H15" s="88"/>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="116" t="s">
+      <c r="A16" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="117"/>
       <c r="E16" s="91"/>
       <c r="F16" s="88"/>
       <c r="G16" s="88"/>
       <c r="H16" s="88"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="116" t="s">
+      <c r="A17" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="117"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
+      <c r="B17" s="116"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="117"/>
       <c r="E17" s="93"/>
       <c r="F17" s="88"/>
       <c r="G17" s="88"/>
       <c r="H17" s="88"/>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="116" t="s">
+      <c r="A18" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="117"/>
       <c r="E18" s="94"/>
       <c r="F18" s="88"/>
       <c r="G18" s="88"/>
       <c r="H18" s="88"/>
     </row>
     <row r="19" spans="1:8" s="96" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="133" t="s">
+      <c r="A19" s="121" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="133"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
       <c r="F19" s="95"/>
       <c r="G19" s="95"/>
       <c r="H19" s="95"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="134" t="s">
+      <c r="A20" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="116" t="s">
+      <c r="B20" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="118"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="117"/>
       <c r="E20" s="97"/>
       <c r="F20" s="88"/>
       <c r="G20" s="88"/>
       <c r="H20" s="88"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="135"/>
-      <c r="B21" s="116" t="s">
+      <c r="A21" s="123"/>
+      <c r="B21" s="115" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="118"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="117"/>
       <c r="E21" s="97"/>
       <c r="F21" s="88"/>
       <c r="G21" s="88"/>
       <c r="H21" s="88"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="116" t="s">
+      <c r="A22" s="123"/>
+      <c r="B22" s="115" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="117"/>
       <c r="E22" s="97"/>
       <c r="F22" s="88"/>
       <c r="G22" s="88"/>
       <c r="H22" s="88"/>
     </row>
     <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="136"/>
-      <c r="B23" s="122" t="s">
+      <c r="A23" s="124"/>
+      <c r="B23" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="123"/>
-      <c r="D23" s="124"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
       <c r="E23" s="97" t="e">
         <f>((E20*(E12-E15))/E12)+E21*E13+E22</f>
         <v>#NUM!</v>
@@ -3688,36 +3691,36 @@
       <c r="H23" s="88"/>
     </row>
     <row r="24" spans="1:8" s="96" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="119" t="s">
+      <c r="A24" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="120"/>
-      <c r="C24" s="120"/>
-      <c r="D24" s="120"/>
-      <c r="E24" s="121"/>
+      <c r="B24" s="126"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="126"/>
+      <c r="E24" s="127"/>
       <c r="F24" s="95"/>
       <c r="G24" s="95"/>
       <c r="H24" s="95"/>
     </row>
     <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="122" t="s">
+      <c r="A25" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="123"/>
-      <c r="C25" s="123"/>
-      <c r="D25" s="124"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="120"/>
       <c r="E25" s="97"/>
       <c r="F25" s="88"/>
       <c r="G25" s="88"/>
       <c r="H25" s="88"/>
     </row>
     <row r="26" spans="1:8" s="96" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="125" t="s">
+      <c r="A26" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="126"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="127"/>
+      <c r="B26" s="129"/>
+      <c r="C26" s="129"/>
+      <c r="D26" s="130"/>
       <c r="E26" s="98" t="e">
         <f>E23-E25</f>
         <v>#NUM!</v>
@@ -3728,6 +3731,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A26:D26"/>
@@ -3743,12 +3752,6 @@
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3810,20 +3813,20 @@
       <c r="E4" s="62"/>
     </row>
     <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.35">
-      <c r="A5" s="115" t="s">
+      <c r="A5" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="115"/>
-      <c r="E5" s="115"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="135"/>
+      <c r="E5" s="135"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="180"/>
-      <c r="C6" s="180"/>
+      <c r="B6" s="205"/>
+      <c r="C6" s="205"/>
       <c r="D6" s="63" t="s">
         <v>26</v>
       </c>
@@ -3836,12 +3839,12 @@
       <c r="A7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="181" t="s">
+      <c r="B7" s="206" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="181"/>
-      <c r="D7" s="181"/>
-      <c r="E7" s="181"/>
+      <c r="C7" s="206"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -3857,24 +3860,24 @@
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="183" t="s">
+      <c r="A9" s="198" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="184"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="185"/>
+      <c r="B9" s="199"/>
+      <c r="C9" s="199"/>
+      <c r="D9" s="200"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="183" t="s">
+      <c r="A10" s="198" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="184"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="185"/>
+      <c r="B10" s="199"/>
+      <c r="C10" s="199"/>
+      <c r="D10" s="200"/>
       <c r="E10" s="7"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -3884,12 +3887,12 @@
       <c r="L10" s="66"/>
     </row>
     <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="183" t="s">
+      <c r="A11" s="198" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="184"/>
-      <c r="C11" s="184"/>
-      <c r="D11" s="185"/>
+      <c r="B11" s="199"/>
+      <c r="C11" s="199"/>
+      <c r="D11" s="200"/>
       <c r="E11" s="7"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
@@ -3902,12 +3905,12 @@
       <c r="L11" s="67"/>
     </row>
     <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="183" t="s">
+      <c r="A12" s="198" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="185"/>
+      <c r="B12" s="199"/>
+      <c r="C12" s="199"/>
+      <c r="D12" s="200"/>
       <c r="E12" s="68"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -3918,13 +3921,13 @@
       <c r="L12" s="67"/>
     </row>
     <row r="13" spans="1:12" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="187" t="s">
+      <c r="A13" s="209" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="187"/>
-      <c r="C13" s="187"/>
-      <c r="D13" s="187"/>
-      <c r="E13" s="187"/>
+      <c r="B13" s="209"/>
+      <c r="C13" s="209"/>
+      <c r="D13" s="209"/>
+      <c r="E13" s="209"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -3933,14 +3936,14 @@
       <c r="L13" s="69"/>
     </row>
     <row r="14" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="182" t="s">
+      <c r="A14" s="207" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="176" t="s">
+      <c r="B14" s="201" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="176"/>
-      <c r="D14" s="176"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="201"/>
       <c r="E14" s="73"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -3951,12 +3954,12 @@
       <c r="L14" s="67"/>
     </row>
     <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="182"/>
-      <c r="B15" s="176" t="s">
+      <c r="A15" s="207"/>
+      <c r="B15" s="201" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="176"/>
-      <c r="D15" s="176"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="201"/>
       <c r="E15" s="74"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -3966,12 +3969,12 @@
       <c r="L15" s="69"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="182"/>
-      <c r="B16" s="183" t="s">
+      <c r="A16" s="207"/>
+      <c r="B16" s="198" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="184"/>
-      <c r="D16" s="185"/>
+      <c r="C16" s="199"/>
+      <c r="D16" s="200"/>
       <c r="E16" s="74"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -3981,12 +3984,12 @@
       <c r="L16" s="69"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="182"/>
-      <c r="B17" s="176" t="s">
+      <c r="A17" s="207"/>
+      <c r="B17" s="201" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="176"/>
-      <c r="D17" s="176"/>
+      <c r="C17" s="201"/>
+      <c r="D17" s="201"/>
       <c r="E17" s="74">
         <f>SUM(E14:E16)</f>
         <v>0</v>
@@ -3996,14 +3999,14 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="186" t="s">
+      <c r="A18" s="208" t="s">
         <v>116</v>
       </c>
-      <c r="B18" s="176" t="s">
+      <c r="B18" s="201" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="176"/>
-      <c r="D18" s="176"/>
+      <c r="C18" s="201"/>
+      <c r="D18" s="201"/>
       <c r="E18" s="74">
         <f>E14*8%</f>
         <v>0</v>
@@ -4013,12 +4016,12 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="186"/>
-      <c r="B19" s="176" t="s">
+      <c r="A19" s="208"/>
+      <c r="B19" s="201" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="176"/>
-      <c r="D19" s="176"/>
+      <c r="C19" s="201"/>
+      <c r="D19" s="201"/>
       <c r="E19" s="74">
         <f>E14*1.5%</f>
         <v>0</v>
@@ -4032,12 +4035,12 @@
       <c r="L19" s="67"/>
     </row>
     <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="186"/>
-      <c r="B20" s="176" t="s">
+      <c r="A20" s="208"/>
+      <c r="B20" s="201" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="176"/>
-      <c r="D20" s="176"/>
+      <c r="C20" s="201"/>
+      <c r="D20" s="201"/>
       <c r="E20" s="74">
         <f>E14*1%</f>
         <v>0</v>
@@ -4047,24 +4050,24 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="186"/>
-      <c r="B21" s="176" t="s">
+      <c r="A21" s="208"/>
+      <c r="B21" s="201" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="176"/>
-      <c r="D21" s="176"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="201"/>
       <c r="E21" s="74"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="186"/>
-      <c r="B22" s="176" t="s">
+      <c r="A22" s="208"/>
+      <c r="B22" s="201" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="176"/>
-      <c r="D22" s="176"/>
+      <c r="C22" s="201"/>
+      <c r="D22" s="201"/>
       <c r="E22" s="74">
         <f>SUM(E18:E21)</f>
         <v>0</v>
@@ -4074,12 +4077,12 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:12" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="177" t="s">
+      <c r="A23" s="202" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="178"/>
-      <c r="C23" s="178"/>
-      <c r="D23" s="179"/>
+      <c r="B23" s="203"/>
+      <c r="C23" s="203"/>
+      <c r="D23" s="204"/>
       <c r="E23" s="75">
         <f>E17-E22</f>
         <v>0</v>
@@ -4100,11 +4103,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B6:C6"/>
@@ -4120,6 +4118,11 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -4129,7 +4132,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A81324B-B4FF-4119-98F2-558A38D65B72}">
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AK61"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.54296875" style="83" customWidth="1"/>
@@ -4157,18 +4160,18 @@
     <col min="25" max="25" width="6.7265625" style="83" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.81640625" style="83" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="8.81640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.81640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="10.36328125" style="83" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.81640625" style="83" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.36328125" style="83" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="9.36328125" style="83" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10.36328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.54296875" style="83" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="7" style="83" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.08984375" style="83" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11.81640625" style="83" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.6328125" style="83" customWidth="1"/>
+    <col min="34" max="34" width="17.453125" style="83" customWidth="1"/>
+    <col min="35" max="35" width="16.81640625" style="83" customWidth="1"/>
+    <col min="36" max="36" width="9.6328125" style="83" customWidth="1"/>
     <col min="37" max="16384" width="8.7265625" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:37" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="18"/>
       <c r="B1" s="19" t="s">
         <v>0</v>
@@ -4181,61 +4184,64 @@
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
       <c r="H1" s="20"/>
-      <c r="L1" s="203" t="s">
+      <c r="L1" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="203" t="s">
+      <c r="M1" s="131" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="203" t="s">
+      <c r="N1" s="131" t="s">
         <v>91</v>
       </c>
-      <c r="O1" s="203" t="s">
+      <c r="O1" s="131" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="206" t="s">
+      <c r="P1" s="141" t="s">
         <v>93</v>
       </c>
-      <c r="Q1" s="195" t="s">
+      <c r="Q1" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="R1" s="198" t="s">
+      <c r="R1" s="147" t="s">
+        <v>119</v>
+      </c>
+      <c r="S1" s="147" t="s">
         <v>95</v>
       </c>
-      <c r="S1" s="198" t="s">
+      <c r="T1" s="147" t="s">
         <v>96</v>
       </c>
-      <c r="T1" s="198" t="s">
+      <c r="U1" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="U1" s="191" t="s">
+      <c r="V1" s="150" t="s">
         <v>98</v>
       </c>
-      <c r="V1" s="188" t="s">
+      <c r="W1" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="W1" s="190"/>
-      <c r="X1" s="190"/>
-      <c r="Y1" s="190"/>
-      <c r="Z1" s="189"/>
-      <c r="AA1" s="188" t="s">
+      <c r="X1" s="154"/>
+      <c r="Y1" s="154"/>
+      <c r="Z1" s="154"/>
+      <c r="AA1" s="155"/>
+      <c r="AB1" s="153" t="s">
         <v>100</v>
       </c>
-      <c r="AB1" s="189"/>
-      <c r="AC1" s="188" t="s">
+      <c r="AC1" s="155"/>
+      <c r="AD1" s="153" t="s">
         <v>101</v>
       </c>
-      <c r="AD1" s="190"/>
-      <c r="AE1" s="190"/>
-      <c r="AF1" s="190"/>
-      <c r="AG1" s="190"/>
-      <c r="AH1" s="190"/>
-      <c r="AI1" s="190"/>
-      <c r="AJ1" s="191" t="s">
+      <c r="AE1" s="154"/>
+      <c r="AF1" s="154"/>
+      <c r="AG1" s="154"/>
+      <c r="AH1" s="154"/>
+      <c r="AI1" s="154"/>
+      <c r="AJ1" s="154"/>
+      <c r="AK1" s="150" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:37" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18"/>
       <c r="B2" s="19" t="s">
         <v>2</v>
@@ -4248,61 +4254,62 @@
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
       <c r="H2" s="20"/>
-      <c r="L2" s="204"/>
-      <c r="M2" s="204"/>
-      <c r="N2" s="204"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="207"/>
-      <c r="Q2" s="196"/>
-      <c r="R2" s="199"/>
-      <c r="S2" s="199"/>
-      <c r="T2" s="199"/>
-      <c r="U2" s="201"/>
-      <c r="V2" s="100" t="s">
+      <c r="L2" s="132"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="132"/>
+      <c r="P2" s="142"/>
+      <c r="Q2" s="145"/>
+      <c r="R2" s="148"/>
+      <c r="S2" s="148"/>
+      <c r="T2" s="148"/>
+      <c r="U2" s="148"/>
+      <c r="V2" s="151"/>
+      <c r="W2" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="W2" s="100" t="s">
+      <c r="X2" s="100" t="s">
         <v>104</v>
       </c>
-      <c r="X2" s="100" t="s">
+      <c r="Y2" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="Y2" s="100" t="s">
+      <c r="Z2" s="100" t="s">
         <v>106</v>
       </c>
-      <c r="Z2" s="194" t="s">
+      <c r="AA2" s="158" t="s">
         <v>107</v>
       </c>
-      <c r="AA2" s="191" t="s">
+      <c r="AB2" s="150" t="s">
         <v>108</v>
       </c>
-      <c r="AB2" s="191" t="s">
+      <c r="AC2" s="150" t="s">
         <v>109</v>
       </c>
-      <c r="AC2" s="100" t="s">
+      <c r="AD2" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="AD2" s="100" t="s">
+      <c r="AE2" s="100" t="s">
         <v>104</v>
       </c>
-      <c r="AE2" s="100" t="s">
+      <c r="AF2" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="AF2" s="191" t="s">
+      <c r="AG2" s="150" t="s">
         <v>110</v>
       </c>
-      <c r="AG2" s="191" t="s">
+      <c r="AH2" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="AH2" s="191" t="s">
+      <c r="AI2" s="150" t="s">
         <v>112</v>
       </c>
-      <c r="AI2" s="191" t="s">
+      <c r="AJ2" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="AJ2" s="192"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="AK2" s="156"/>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" s="18"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19" t="s">
@@ -4313,47 +4320,48 @@
       <c r="F3" s="18"/>
       <c r="G3" s="18"/>
       <c r="H3" s="20"/>
-      <c r="L3" s="205"/>
-      <c r="M3" s="205"/>
-      <c r="N3" s="205"/>
-      <c r="O3" s="205"/>
-      <c r="P3" s="208"/>
-      <c r="Q3" s="197"/>
-      <c r="R3" s="200"/>
-      <c r="S3" s="200"/>
-      <c r="T3" s="200"/>
-      <c r="U3" s="202"/>
-      <c r="V3" s="101">
+      <c r="L3" s="133"/>
+      <c r="M3" s="133"/>
+      <c r="N3" s="133"/>
+      <c r="O3" s="133"/>
+      <c r="P3" s="143"/>
+      <c r="Q3" s="146"/>
+      <c r="R3" s="149"/>
+      <c r="S3" s="149"/>
+      <c r="T3" s="149"/>
+      <c r="U3" s="149"/>
+      <c r="V3" s="152"/>
+      <c r="W3" s="101">
         <v>0.17499999999999999</v>
       </c>
-      <c r="W3" s="101">
+      <c r="X3" s="101">
         <v>0.03</v>
       </c>
-      <c r="X3" s="101">
+      <c r="Y3" s="101">
         <v>0.01</v>
       </c>
-      <c r="Y3" s="101">
+      <c r="Z3" s="101">
         <v>0.02</v>
       </c>
-      <c r="Z3" s="193"/>
-      <c r="AA3" s="193"/>
-      <c r="AB3" s="193"/>
-      <c r="AC3" s="101">
+      <c r="AA3" s="157"/>
+      <c r="AB3" s="157"/>
+      <c r="AC3" s="157"/>
+      <c r="AD3" s="101">
         <v>0.08</v>
       </c>
-      <c r="AD3" s="101">
+      <c r="AE3" s="101">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AE3" s="101">
+      <c r="AF3" s="101">
         <v>0.01</v>
       </c>
-      <c r="AF3" s="193"/>
-      <c r="AG3" s="193"/>
-      <c r="AH3" s="193"/>
-      <c r="AI3" s="193"/>
-      <c r="AJ3" s="193"/>
-    </row>
-    <row r="4" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AG3" s="157"/>
+      <c r="AH3" s="157"/>
+      <c r="AI3" s="157"/>
+      <c r="AJ3" s="157"/>
+      <c r="AK3" s="157"/>
+    </row>
+    <row r="4" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="18"/>
       <c r="B4" s="19" t="s">
         <v>5</v>
@@ -4381,56 +4389,57 @@
       <c r="R4" s="107"/>
       <c r="S4" s="107"/>
       <c r="T4" s="107"/>
-      <c r="U4" s="107">
+      <c r="U4" s="107"/>
+      <c r="V4" s="107">
         <v>11</v>
       </c>
-      <c r="V4" s="107">
+      <c r="W4" s="107">
         <v>12</v>
       </c>
-      <c r="W4" s="107">
+      <c r="X4" s="107">
         <v>13</v>
       </c>
-      <c r="X4" s="107">
+      <c r="Y4" s="107">
         <v>14</v>
       </c>
-      <c r="Y4" s="107">
+      <c r="Z4" s="107">
         <v>15</v>
       </c>
-      <c r="Z4" s="107">
+      <c r="AA4" s="107">
         <v>16</v>
       </c>
-      <c r="AA4" s="107">
+      <c r="AB4" s="107">
         <v>17</v>
       </c>
-      <c r="AB4" s="107">
+      <c r="AC4" s="107">
         <v>18</v>
       </c>
-      <c r="AC4" s="107">
+      <c r="AD4" s="107">
         <v>19</v>
       </c>
-      <c r="AD4" s="107">
+      <c r="AE4" s="107">
         <v>20</v>
       </c>
-      <c r="AE4" s="107">
+      <c r="AF4" s="107">
         <v>21</v>
       </c>
-      <c r="AF4" s="107">
+      <c r="AG4" s="107">
         <v>22</v>
       </c>
-      <c r="AG4" s="107">
+      <c r="AH4" s="107">
         <v>23</v>
       </c>
-      <c r="AH4" s="108">
+      <c r="AI4" s="108">
         <v>24</v>
       </c>
-      <c r="AI4" s="107">
+      <c r="AJ4" s="107">
         <v>25</v>
       </c>
-      <c r="AJ4" s="107">
+      <c r="AK4" s="107">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" s="18"/>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -4445,182 +4454,187 @@
       <c r="O5" s="110">
         <v>26</v>
       </c>
-      <c r="P5" s="111">
-        <f>Q7</f>
-        <v>0</v>
-      </c>
+      <c r="P5" s="111"/>
       <c r="Q5" s="112"/>
       <c r="R5" s="111">
-        <f>P5+Q5</f>
         <v>0</v>
       </c>
       <c r="S5" s="111">
+        <f>((P5/O5)*O5)+SUM(Q5:R5)</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="111">
+        <f>S5-Q5</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="111">
+        <v>0</v>
+      </c>
+      <c r="V5" s="111">
         <f>P5</f>
         <v>0</v>
       </c>
-      <c r="T5" s="111">
-        <v>0</v>
-      </c>
-      <c r="U5" s="111">
-        <f>P5</f>
-        <v>0</v>
-      </c>
-      <c r="V5" s="111">
-        <f>U5*V3</f>
-        <v>0</v>
-      </c>
       <c r="W5" s="103">
-        <f>U5*W3</f>
+        <f>V5*W3</f>
         <v>0</v>
       </c>
       <c r="X5" s="103">
-        <f>U5*X3</f>
+        <f>V5*X3</f>
         <v>0</v>
       </c>
       <c r="Y5" s="103">
+        <f>V5*Y3</f>
         <v>0</v>
       </c>
       <c r="Z5" s="103">
-        <f>SUM(V5:X5)</f>
-        <v>0</v>
-      </c>
-      <c r="AA5" s="103"/>
-      <c r="AB5" s="103">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="103">
+        <f>SUM(W5:Y5)</f>
+        <v>0</v>
+      </c>
+      <c r="AB5" s="103"/>
+      <c r="AC5" s="103">
         <v>15500000</v>
       </c>
-      <c r="AC5" s="103">
-        <f>U5*AC3</f>
-        <v>0</v>
-      </c>
       <c r="AD5" s="103">
-        <f>U5*AD3</f>
+        <f>V5*AD3</f>
         <v>0</v>
       </c>
       <c r="AE5" s="103">
-        <f>U5*AE3</f>
+        <f>V5*AE3</f>
         <v>0</v>
       </c>
       <c r="AF5" s="103">
-        <f>SUM(AC5:AE5)</f>
+        <f>V5*AF3</f>
         <v>0</v>
       </c>
       <c r="AG5" s="103">
+        <f>SUM(AD5:AF5)</f>
         <v>0</v>
       </c>
       <c r="AH5" s="103">
+        <f>MAX(T5-AB5-AC5-AG5,0)</f>
         <v>0</v>
       </c>
       <c r="AI5" s="103">
+        <f>MIN(AH5,10000000)*0.05+MAX(MIN(AH5-10000000,20000000),0)*0.1+MAX(MIN(AH5-30000000,30000000),0)*0.2+MAX(MIN(AH5-60000000,40000000),0)*0.3+MAX(AH5-100000000,0)*0.35</f>
         <v>0</v>
       </c>
       <c r="AJ5" s="103">
-        <f>R5+T5-AF5-AH5-AI5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="174" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="103">
+        <f>S5+U5-AG5-AI5-AJ5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" ht="25" x14ac:dyDescent="0.35">
+      <c r="A6" s="161" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="174"/>
-      <c r="C6" s="174"/>
-      <c r="D6" s="174"/>
-      <c r="E6" s="174"/>
-      <c r="F6" s="174"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="174"/>
-    </row>
-    <row r="7" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B6" s="161"/>
+      <c r="C6" s="161"/>
+      <c r="D6" s="161"/>
+      <c r="E6" s="161"/>
+      <c r="F6" s="161"/>
+      <c r="G6" s="161"/>
+      <c r="H6" s="161"/>
+    </row>
+    <row r="7" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="172"/>
-      <c r="C7" s="172"/>
+      <c r="B7" s="159"/>
+      <c r="C7" s="159"/>
       <c r="D7" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="175"/>
-      <c r="F7" s="175"/>
-      <c r="G7" s="175"/>
-      <c r="H7" s="175"/>
-      <c r="O7" s="209" t="s">
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="162"/>
+      <c r="O7" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="P7" s="209"/>
-      <c r="Q7" s="114"/>
+      <c r="P7" s="134"/>
+      <c r="Q7" s="114">
+        <f>AK5</f>
+        <v>0</v>
+      </c>
       <c r="R7" s="113"/>
     </row>
-    <row r="8" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="172"/>
-      <c r="C8" s="172"/>
+      <c r="B8" s="159"/>
+      <c r="C8" s="159"/>
       <c r="D8" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="172" t="s">
+      <c r="E8" s="159" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="172"/>
-      <c r="G8" s="172"/>
-      <c r="H8" s="172"/>
-      <c r="O8" s="209" t="s">
+      <c r="F8" s="159"/>
+      <c r="G8" s="159"/>
+      <c r="H8" s="159"/>
+      <c r="O8" s="134" t="s">
         <v>115</v>
       </c>
-      <c r="P8" s="209"/>
+      <c r="P8" s="134"/>
       <c r="Q8" s="114">
         <f>H61-Q7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="172" t="s">
+      <c r="B9" s="159" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="172"/>
+      <c r="C9" s="159"/>
       <c r="D9" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="172" t="s">
+      <c r="E9" s="159" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="172"/>
-      <c r="G9" s="172"/>
-      <c r="H9" s="172"/>
-    </row>
-    <row r="10" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="F9" s="159"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="159"/>
+    </row>
+    <row r="10" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="172"/>
-      <c r="C10" s="172"/>
+      <c r="B10" s="159"/>
+      <c r="C10" s="159"/>
       <c r="D10" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="172"/>
-      <c r="F10" s="172"/>
-      <c r="G10" s="172"/>
-      <c r="H10" s="172"/>
-    </row>
-    <row r="11" spans="1:36" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E10" s="159"/>
+      <c r="F10" s="159"/>
+      <c r="G10" s="159"/>
+      <c r="H10" s="159"/>
+    </row>
+    <row r="11" spans="1:37" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="23">
         <v>1</v>
       </c>
-      <c r="B11" s="173" t="s">
+      <c r="B11" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="173"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="173"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="173"/>
-      <c r="H11" s="173"/>
-    </row>
-    <row r="12" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="C11" s="160"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+    </row>
+    <row r="12" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="25" t="s">
         <v>33</v>
       </c>
@@ -4634,7 +4648,7 @@
       <c r="G12" s="164"/>
       <c r="H12" s="165"/>
     </row>
-    <row r="13" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
         <v>35</v>
       </c>
@@ -4648,7 +4662,7 @@
       <c r="G13" s="166"/>
       <c r="H13" s="167"/>
     </row>
-    <row r="14" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="26" t="s">
         <v>37</v>
       </c>
@@ -4662,7 +4676,7 @@
       <c r="G14" s="166"/>
       <c r="H14" s="167"/>
     </row>
-    <row r="15" spans="1:36" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="26" t="s">
         <v>39</v>
       </c>
@@ -4680,7 +4694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:37" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="27" t="s">
         <v>41</v>
       </c>
@@ -4892,12 +4906,12 @@
     </row>
     <row r="31" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A31" s="43"/>
-      <c r="B31" s="155" t="s">
+      <c r="B31" s="179" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="155"/>
-      <c r="D31" s="155"/>
-      <c r="E31" s="155"/>
+      <c r="C31" s="179"/>
+      <c r="D31" s="179"/>
+      <c r="E31" s="179"/>
       <c r="F31" s="13">
         <f>SUM(F21:F30)</f>
         <v>0</v>
@@ -5006,12 +5020,12 @@
     </row>
     <row r="39" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A39" s="43"/>
-      <c r="B39" s="156" t="s">
+      <c r="B39" s="180" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="157"/>
-      <c r="D39" s="157"/>
-      <c r="E39" s="157"/>
+      <c r="C39" s="181"/>
+      <c r="D39" s="181"/>
+      <c r="E39" s="181"/>
       <c r="F39" s="16">
         <f>SUM(F37:F38)</f>
         <v>0</v>
@@ -5089,13 +5103,13 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="156" t="s">
+      <c r="A44" s="180" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="157"/>
-      <c r="C44" s="157"/>
-      <c r="D44" s="157"/>
-      <c r="E44" s="158"/>
+      <c r="B44" s="181"/>
+      <c r="C44" s="181"/>
+      <c r="D44" s="181"/>
+      <c r="E44" s="182"/>
       <c r="F44" s="16">
         <f>SUM(F42:F43)</f>
         <v>0</v>
@@ -5173,13 +5187,13 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="156" t="s">
+      <c r="A49" s="180" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="157"/>
-      <c r="C49" s="157"/>
-      <c r="D49" s="157"/>
-      <c r="E49" s="158"/>
+      <c r="B49" s="181"/>
+      <c r="C49" s="181"/>
+      <c r="D49" s="181"/>
+      <c r="E49" s="182"/>
       <c r="F49" s="16">
         <f>SUM(F47:F48)</f>
         <v>0</v>
@@ -5217,23 +5231,23 @@
       <c r="D51" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="155" t="s">
+      <c r="E51" s="179" t="s">
         <v>20</v>
       </c>
-      <c r="F51" s="155"/>
-      <c r="G51" s="155"/>
+      <c r="F51" s="179"/>
+      <c r="G51" s="179"/>
       <c r="H51" s="50"/>
     </row>
     <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="159" t="s">
+      <c r="A52" s="172" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="160"/>
-      <c r="C52" s="160"/>
-      <c r="D52" s="160"/>
-      <c r="E52" s="160"/>
-      <c r="F52" s="160"/>
-      <c r="G52" s="161"/>
+      <c r="B52" s="173"/>
+      <c r="C52" s="173"/>
+      <c r="D52" s="173"/>
+      <c r="E52" s="173"/>
+      <c r="F52" s="173"/>
+      <c r="G52" s="174"/>
       <c r="H52" s="59">
         <v>0</v>
       </c>
@@ -5242,10 +5256,10 @@
       <c r="A53" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="162" t="s">
+      <c r="B53" s="175" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="162"/>
+      <c r="C53" s="175"/>
       <c r="D53" s="51"/>
       <c r="E53" s="52"/>
       <c r="F53" s="52"/>
@@ -5253,61 +5267,61 @@
       <c r="H53" s="53"/>
     </row>
     <row r="54" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="176" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="145"/>
-      <c r="C54" s="145"/>
-      <c r="D54" s="145"/>
-      <c r="E54" s="146"/>
-      <c r="F54" s="138">
-        <v>0</v>
-      </c>
-      <c r="G54" s="139"/>
-      <c r="H54" s="140"/>
+      <c r="B54" s="177"/>
+      <c r="C54" s="177"/>
+      <c r="D54" s="177"/>
+      <c r="E54" s="178"/>
+      <c r="F54" s="184">
+        <v>0</v>
+      </c>
+      <c r="G54" s="185"/>
+      <c r="H54" s="186"/>
     </row>
     <row r="55" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="176" t="s">
         <v>71</v>
       </c>
-      <c r="B55" s="145"/>
-      <c r="C55" s="145"/>
-      <c r="D55" s="145"/>
-      <c r="E55" s="146"/>
-      <c r="F55" s="138">
-        <v>0</v>
-      </c>
-      <c r="G55" s="139"/>
-      <c r="H55" s="140"/>
+      <c r="B55" s="177"/>
+      <c r="C55" s="177"/>
+      <c r="D55" s="177"/>
+      <c r="E55" s="178"/>
+      <c r="F55" s="184">
+        <v>0</v>
+      </c>
+      <c r="G55" s="185"/>
+      <c r="H55" s="186"/>
     </row>
     <row r="56" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="176" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="145"/>
-      <c r="C56" s="145"/>
-      <c r="D56" s="145"/>
-      <c r="E56" s="146"/>
-      <c r="F56" s="138">
-        <v>0</v>
-      </c>
-      <c r="G56" s="139"/>
-      <c r="H56" s="140"/>
+      <c r="B56" s="177"/>
+      <c r="C56" s="177"/>
+      <c r="D56" s="177"/>
+      <c r="E56" s="178"/>
+      <c r="F56" s="184">
+        <v>0</v>
+      </c>
+      <c r="G56" s="185"/>
+      <c r="H56" s="186"/>
     </row>
     <row r="57" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="155" t="s">
+      <c r="A57" s="179" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="155"/>
-      <c r="C57" s="155"/>
-      <c r="D57" s="155"/>
-      <c r="E57" s="155"/>
-      <c r="F57" s="141">
+      <c r="B57" s="179"/>
+      <c r="C57" s="179"/>
+      <c r="D57" s="179"/>
+      <c r="E57" s="179"/>
+      <c r="F57" s="187">
         <f>F54+F55*F56</f>
         <v>0</v>
       </c>
-      <c r="G57" s="142"/>
-      <c r="H57" s="143"/>
+      <c r="G57" s="188"/>
+      <c r="H57" s="189"/>
     </row>
     <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A58" s="54"/>
@@ -5323,36 +5337,36 @@
       <c r="A59" s="55">
         <v>3</v>
       </c>
-      <c r="B59" s="153" t="s">
+      <c r="B59" s="196" t="s">
         <v>68</v>
       </c>
-      <c r="C59" s="154"/>
-      <c r="D59" s="147"/>
-      <c r="E59" s="148"/>
-      <c r="F59" s="148"/>
-      <c r="G59" s="148"/>
-      <c r="H59" s="149"/>
+      <c r="C59" s="197"/>
+      <c r="D59" s="190"/>
+      <c r="E59" s="191"/>
+      <c r="F59" s="191"/>
+      <c r="G59" s="191"/>
+      <c r="H59" s="192"/>
     </row>
     <row r="60" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="147" t="s">
+      <c r="A60" s="190" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="148"/>
-      <c r="C60" s="149"/>
-      <c r="D60" s="150"/>
-      <c r="E60" s="151"/>
-      <c r="F60" s="151"/>
-      <c r="G60" s="151"/>
-      <c r="H60" s="152"/>
+      <c r="B60" s="191"/>
+      <c r="C60" s="192"/>
+      <c r="D60" s="193"/>
+      <c r="E60" s="194"/>
+      <c r="F60" s="194"/>
+      <c r="G60" s="194"/>
+      <c r="H60" s="195"/>
     </row>
     <row r="61" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A61" s="56">
         <v>4</v>
       </c>
-      <c r="B61" s="137" t="s">
+      <c r="B61" s="183" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="137"/>
+      <c r="C61" s="183"/>
       <c r="D61" s="57"/>
       <c r="E61" s="57"/>
       <c r="F61" s="57"/>
@@ -5363,22 +5377,40 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="63">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="B13:C13"/>
+  <mergeCells count="64">
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
+    <mergeCell ref="V1:V3"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AJ1"/>
+    <mergeCell ref="Q1:Q3"/>
+    <mergeCell ref="R1:R3"/>
+    <mergeCell ref="S1:S3"/>
+    <mergeCell ref="T1:T3"/>
+    <mergeCell ref="U1:U3"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="L1:L3"/>
+    <mergeCell ref="M1:M3"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="O1:O3"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="D60:H60"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:H15"/>
     <mergeCell ref="P1:P3"/>
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="O7:P7"/>
@@ -5395,38 +5427,21 @@
     <mergeCell ref="B39:E39"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A49:E49"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="L1:L3"/>
-    <mergeCell ref="M1:M3"/>
-    <mergeCell ref="N1:N3"/>
-    <mergeCell ref="O1:O3"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="Q1:Q3"/>
-    <mergeCell ref="R1:R3"/>
-    <mergeCell ref="S1:S3"/>
-    <mergeCell ref="T1:T3"/>
-    <mergeCell ref="U1:U3"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AC1:AI1"/>
-    <mergeCell ref="AJ1:AJ3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
-    <mergeCell ref="V1:Z1"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B13:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B8" xr:uid="{82479240-5D3B-410A-AD98-6642A9B2C328}">
@@ -5440,7 +5455,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE48A5E-E284-4325-8D9D-69C0CC780F2C}">
-  <dimension ref="A1:AG36"/>
+  <dimension ref="A1:AH36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.08984375" customWidth="1"/>
@@ -5452,27 +5467,27 @@
     <col min="12" max="12" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.1796875" customWidth="1"/>
+    <col min="16" max="16" width="24.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="21.08984375" customWidth="1"/>
+    <col min="33" max="33" width="9.08984375" customWidth="1"/>
+    <col min="34" max="34" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" s="80"/>
       <c r="B1" s="81" t="s">
         <v>0</v>
@@ -5482,61 +5497,64 @@
       </c>
       <c r="D1" s="80"/>
       <c r="E1" s="82"/>
-      <c r="I1" s="203" t="s">
+      <c r="I1" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="203" t="s">
+      <c r="J1" s="131" t="s">
         <v>90</v>
       </c>
-      <c r="K1" s="203" t="s">
+      <c r="K1" s="131" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="203" t="s">
+      <c r="L1" s="131" t="s">
         <v>92</v>
       </c>
-      <c r="M1" s="206" t="s">
+      <c r="M1" s="141" t="s">
         <v>93</v>
       </c>
-      <c r="N1" s="195" t="s">
+      <c r="N1" s="144" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="198" t="s">
+      <c r="O1" s="147" t="s">
+        <v>119</v>
+      </c>
+      <c r="P1" s="147" t="s">
         <v>95</v>
       </c>
-      <c r="P1" s="198" t="s">
+      <c r="Q1" s="147" t="s">
         <v>96</v>
       </c>
-      <c r="Q1" s="198" t="s">
+      <c r="R1" s="147" t="s">
         <v>97</v>
       </c>
-      <c r="R1" s="191" t="s">
+      <c r="S1" s="150" t="s">
         <v>98</v>
       </c>
-      <c r="S1" s="188" t="s">
+      <c r="T1" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="T1" s="190"/>
-      <c r="U1" s="190"/>
-      <c r="V1" s="190"/>
-      <c r="W1" s="189"/>
-      <c r="X1" s="188" t="s">
+      <c r="U1" s="154"/>
+      <c r="V1" s="154"/>
+      <c r="W1" s="154"/>
+      <c r="X1" s="155"/>
+      <c r="Y1" s="153" t="s">
         <v>100</v>
       </c>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="188" t="s">
+      <c r="Z1" s="155"/>
+      <c r="AA1" s="153" t="s">
         <v>101</v>
       </c>
-      <c r="AA1" s="190"/>
-      <c r="AB1" s="190"/>
-      <c r="AC1" s="190"/>
-      <c r="AD1" s="190"/>
-      <c r="AE1" s="190"/>
-      <c r="AF1" s="190"/>
-      <c r="AG1" s="191" t="s">
+      <c r="AB1" s="154"/>
+      <c r="AC1" s="154"/>
+      <c r="AD1" s="154"/>
+      <c r="AE1" s="154"/>
+      <c r="AF1" s="154"/>
+      <c r="AG1" s="154"/>
+      <c r="AH1" s="150" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" s="80"/>
       <c r="B2" s="81" t="s">
         <v>2</v>
@@ -5546,61 +5564,62 @@
       </c>
       <c r="D2" s="80"/>
       <c r="E2" s="82"/>
-      <c r="I2" s="204"/>
-      <c r="J2" s="204"/>
-      <c r="K2" s="204"/>
-      <c r="L2" s="204"/>
-      <c r="M2" s="207"/>
-      <c r="N2" s="196"/>
-      <c r="O2" s="199"/>
-      <c r="P2" s="199"/>
-      <c r="Q2" s="199"/>
-      <c r="R2" s="201"/>
-      <c r="S2" s="100" t="s">
+      <c r="I2" s="132"/>
+      <c r="J2" s="132"/>
+      <c r="K2" s="132"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="142"/>
+      <c r="N2" s="145"/>
+      <c r="O2" s="148"/>
+      <c r="P2" s="148"/>
+      <c r="Q2" s="148"/>
+      <c r="R2" s="148"/>
+      <c r="S2" s="151"/>
+      <c r="T2" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="T2" s="100" t="s">
+      <c r="U2" s="100" t="s">
         <v>104</v>
       </c>
-      <c r="U2" s="100" t="s">
+      <c r="V2" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="V2" s="100" t="s">
+      <c r="W2" s="100" t="s">
         <v>106</v>
       </c>
-      <c r="W2" s="194" t="s">
+      <c r="X2" s="158" t="s">
         <v>107</v>
       </c>
-      <c r="X2" s="191" t="s">
+      <c r="Y2" s="150" t="s">
         <v>108</v>
       </c>
-      <c r="Y2" s="191" t="s">
+      <c r="Z2" s="150" t="s">
         <v>109</v>
       </c>
-      <c r="Z2" s="100" t="s">
+      <c r="AA2" s="100" t="s">
         <v>103</v>
       </c>
-      <c r="AA2" s="100" t="s">
+      <c r="AB2" s="100" t="s">
         <v>104</v>
       </c>
-      <c r="AB2" s="100" t="s">
+      <c r="AC2" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="AC2" s="191" t="s">
+      <c r="AD2" s="150" t="s">
         <v>110</v>
       </c>
-      <c r="AD2" s="191" t="s">
+      <c r="AE2" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="AE2" s="191" t="s">
+      <c r="AF2" s="150" t="s">
         <v>112</v>
       </c>
-      <c r="AF2" s="191" t="s">
+      <c r="AG2" s="150" t="s">
         <v>113</v>
       </c>
-      <c r="AG2" s="192"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AH2" s="156"/>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" s="80"/>
       <c r="B3" s="81"/>
       <c r="C3" s="81" t="s">
@@ -5608,47 +5627,48 @@
       </c>
       <c r="D3" s="80"/>
       <c r="E3" s="82"/>
-      <c r="I3" s="205"/>
-      <c r="J3" s="205"/>
-      <c r="K3" s="205"/>
-      <c r="L3" s="205"/>
-      <c r="M3" s="208"/>
-      <c r="N3" s="197"/>
-      <c r="O3" s="200"/>
-      <c r="P3" s="200"/>
-      <c r="Q3" s="200"/>
-      <c r="R3" s="202"/>
-      <c r="S3" s="101">
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="146"/>
+      <c r="O3" s="149"/>
+      <c r="P3" s="149"/>
+      <c r="Q3" s="149"/>
+      <c r="R3" s="149"/>
+      <c r="S3" s="152"/>
+      <c r="T3" s="101">
         <v>0.17499999999999999</v>
       </c>
-      <c r="T3" s="101">
+      <c r="U3" s="101">
         <v>0.03</v>
       </c>
-      <c r="U3" s="101">
+      <c r="V3" s="101">
         <v>0.01</v>
       </c>
-      <c r="V3" s="101">
+      <c r="W3" s="101">
         <v>0.02</v>
       </c>
-      <c r="W3" s="193"/>
-      <c r="X3" s="193"/>
-      <c r="Y3" s="193"/>
-      <c r="Z3" s="101">
+      <c r="X3" s="157"/>
+      <c r="Y3" s="157"/>
+      <c r="Z3" s="157"/>
+      <c r="AA3" s="101">
         <v>0.08</v>
       </c>
-      <c r="AA3" s="101">
+      <c r="AB3" s="101">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AB3" s="101">
+      <c r="AC3" s="101">
         <v>0.01</v>
       </c>
-      <c r="AC3" s="193"/>
-      <c r="AD3" s="193"/>
-      <c r="AE3" s="193"/>
-      <c r="AF3" s="193"/>
-      <c r="AG3" s="193"/>
-    </row>
-    <row r="4" spans="1:33" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AD3" s="157"/>
+      <c r="AE3" s="157"/>
+      <c r="AF3" s="157"/>
+      <c r="AG3" s="157"/>
+      <c r="AH3" s="157"/>
+    </row>
+    <row r="4" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="80"/>
       <c r="B4" s="81" t="s">
         <v>5</v>
@@ -5673,56 +5693,57 @@
       <c r="O4" s="107"/>
       <c r="P4" s="107"/>
       <c r="Q4" s="107"/>
-      <c r="R4" s="107">
+      <c r="R4" s="107"/>
+      <c r="S4" s="107">
         <v>11</v>
       </c>
-      <c r="S4" s="107">
+      <c r="T4" s="107">
         <v>12</v>
       </c>
-      <c r="T4" s="107">
+      <c r="U4" s="107">
         <v>13</v>
       </c>
-      <c r="U4" s="107">
+      <c r="V4" s="107">
         <v>14</v>
       </c>
-      <c r="V4" s="107">
+      <c r="W4" s="107">
         <v>15</v>
       </c>
-      <c r="W4" s="107">
+      <c r="X4" s="107">
         <v>16</v>
       </c>
-      <c r="X4" s="107">
+      <c r="Y4" s="107">
         <v>17</v>
       </c>
-      <c r="Y4" s="107">
+      <c r="Z4" s="107">
         <v>18</v>
       </c>
-      <c r="Z4" s="107">
+      <c r="AA4" s="107">
         <v>19</v>
       </c>
-      <c r="AA4" s="107">
+      <c r="AB4" s="107">
         <v>20</v>
       </c>
-      <c r="AB4" s="107">
+      <c r="AC4" s="107">
         <v>21</v>
       </c>
-      <c r="AC4" s="107">
+      <c r="AD4" s="107">
         <v>22</v>
       </c>
-      <c r="AD4" s="107">
+      <c r="AE4" s="107">
         <v>23</v>
       </c>
-      <c r="AE4" s="108">
+      <c r="AF4" s="108">
         <v>24</v>
       </c>
-      <c r="AF4" s="107">
+      <c r="AG4" s="107">
         <v>25</v>
       </c>
-      <c r="AG4" s="107">
+      <c r="AH4" s="107">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" s="80"/>
       <c r="B5" s="80"/>
       <c r="C5" s="80"/>
@@ -5734,87 +5755,89 @@
       <c r="L5" s="110">
         <v>26</v>
       </c>
-      <c r="M5" s="111">
-        <f>N7</f>
-        <v>0</v>
-      </c>
+      <c r="M5" s="111"/>
       <c r="N5" s="112"/>
       <c r="O5" s="111">
-        <f>M5+N5</f>
         <v>0</v>
       </c>
       <c r="P5" s="111">
+        <f>((M5/L5)*L5)+SUM(N5:O5)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="111">
+        <f>P5-N5</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="111">
+        <v>0</v>
+      </c>
+      <c r="S5" s="111">
         <f>M5</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="111">
-        <v>0</v>
-      </c>
-      <c r="R5" s="111">
-        <f>M5</f>
-        <v>0</v>
-      </c>
-      <c r="S5" s="103">
-        <f>R5*S3</f>
-        <v>0</v>
-      </c>
       <c r="T5" s="103">
-        <f>R5*T3</f>
+        <f>S5*T3</f>
         <v>0</v>
       </c>
       <c r="U5" s="103">
-        <f>R5*U3</f>
+        <f>S5*U3</f>
         <v>0</v>
       </c>
       <c r="V5" s="103">
+        <f>S5*V3</f>
         <v>0</v>
       </c>
       <c r="W5" s="103">
-        <f>SUM(S5:U5)</f>
-        <v>0</v>
-      </c>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="103">
+        <v>0</v>
+      </c>
+      <c r="X5" s="103">
+        <f>SUM(T5:V5)</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="103"/>
+      <c r="Z5" s="103">
         <v>15500000</v>
       </c>
-      <c r="Z5" s="103">
-        <f>R5*Z3</f>
-        <v>0</v>
-      </c>
       <c r="AA5" s="103">
-        <f>R5*AA3</f>
+        <f>S5*AA3</f>
         <v>0</v>
       </c>
       <c r="AB5" s="103">
-        <f>R5*AB3</f>
+        <f>S5*AB3</f>
         <v>0</v>
       </c>
       <c r="AC5" s="103">
-        <f>SUM(Z5:AB5)</f>
+        <f>S5*AC3</f>
         <v>0</v>
       </c>
       <c r="AD5" s="103">
+        <f>SUM(AA5:AC5)</f>
         <v>0</v>
       </c>
       <c r="AE5" s="103">
+        <f>MAX(Q5-Y5-Z5-AD5,0)</f>
         <v>0</v>
       </c>
       <c r="AF5" s="103">
+        <f>MIN(AE5,10000000)*0.05+MAX(MIN(AE5-10000000,20000000),0)*0.1+MAX(MIN(AE5-30000000,30000000),0)*0.2+MAX(MIN(AE5-60000000,40000000),0)*0.3+MAX(AE5-100000000,0)*0.35</f>
         <v>0</v>
       </c>
       <c r="AG5" s="103">
-        <f>O5+Q5-AC5-AE5-AF5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="115" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="103">
+        <f>P5+R5-AD5-AF5-AG5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" ht="25" x14ac:dyDescent="0.35">
+      <c r="A6" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="135"/>
+      <c r="E6" s="135"/>
       <c r="I6" s="83"/>
       <c r="J6" s="83"/>
       <c r="K6" s="83"/>
@@ -5840,13 +5863,14 @@
       <c r="AE6" s="83"/>
       <c r="AF6" s="83"/>
       <c r="AG6" s="83"/>
-    </row>
-    <row r="7" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="AH6" s="83"/>
+    </row>
+    <row r="7" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="128"/>
-      <c r="C7" s="129"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="137"/>
       <c r="D7" s="86" t="s">
         <v>73</v>
       </c>
@@ -5857,13 +5881,16 @@
       <c r="I7" s="83"/>
       <c r="J7" s="83"/>
       <c r="K7" s="83"/>
-      <c r="L7" s="209" t="s">
+      <c r="L7" s="134" t="s">
         <v>114</v>
       </c>
-      <c r="M7" s="209"/>
-      <c r="N7" s="114"/>
-      <c r="O7" s="113"/>
-      <c r="P7" s="83"/>
+      <c r="M7" s="134"/>
+      <c r="N7" s="114">
+        <f>AH5</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="114"/>
+      <c r="P7" s="113"/>
       <c r="Q7" s="83"/>
       <c r="R7" s="83"/>
       <c r="S7" s="83"/>
@@ -5881,32 +5908,33 @@
       <c r="AE7" s="83"/>
       <c r="AF7" s="83"/>
       <c r="AG7" s="83"/>
-    </row>
-    <row r="8" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="AH7" s="83"/>
+    </row>
+    <row r="8" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="130" t="s">
+      <c r="B8" s="138" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="131"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="132"/>
+      <c r="C8" s="139"/>
+      <c r="D8" s="139"/>
+      <c r="E8" s="140"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="83"/>
       <c r="J8" s="83"/>
       <c r="K8" s="83"/>
-      <c r="L8" s="209" t="s">
+      <c r="L8" s="134" t="s">
         <v>115</v>
       </c>
-      <c r="M8" s="209"/>
+      <c r="M8" s="134"/>
       <c r="N8" s="114" t="e">
         <f>E26-N7</f>
         <v>#NUM!</v>
       </c>
-      <c r="O8" s="83"/>
+      <c r="O8" s="114"/>
       <c r="P8" s="83"/>
       <c r="Q8" s="83"/>
       <c r="R8" s="83"/>
@@ -5925,8 +5953,9 @@
       <c r="AE8" s="83"/>
       <c r="AF8" s="83"/>
       <c r="AG8" s="83"/>
-    </row>
-    <row r="9" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="AH8" s="83"/>
+    </row>
+    <row r="9" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="89"/>
       <c r="B9" s="89"/>
       <c r="C9" s="89"/>
@@ -5936,37 +5965,37 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="116" t="s">
+    <row r="10" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="117"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="117"/>
       <c r="E10" s="91"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="116" t="s">
+    <row r="11" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="117"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="118"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="117"/>
       <c r="E11" s="91"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="116" t="s">
+    <row r="12" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="117"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="118"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="117"/>
       <c r="E12" s="92" t="e">
         <f>DAY(EOMONTH(DATE(E7,B7,1),0))</f>
         <v>#NUM!</v>
@@ -5975,135 +6004,135 @@
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="116" t="s">
+    <row r="13" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="115" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="117"/>
       <c r="E13" s="91"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="116" t="s">
+    <row r="14" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="118"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="116"/>
+      <c r="D14" s="117"/>
       <c r="E14" s="91"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="116" t="s">
+    <row r="15" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="117"/>
       <c r="E15" s="91"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:33" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="116" t="s">
+    <row r="16" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="117"/>
       <c r="E16" s="91"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="116" t="s">
+      <c r="A17" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="117"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
+      <c r="B17" s="116"/>
+      <c r="C17" s="116"/>
+      <c r="D17" s="117"/>
       <c r="E17" s="93"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="116" t="s">
+      <c r="A18" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
+      <c r="B18" s="116"/>
+      <c r="C18" s="116"/>
+      <c r="D18" s="117"/>
       <c r="E18" s="94"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="133" t="s">
+      <c r="A19" s="121" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="133"/>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
+      <c r="B19" s="121"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="134" t="s">
+      <c r="A20" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="116" t="s">
+      <c r="B20" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="118"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="117"/>
       <c r="E20" s="97"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="135"/>
-      <c r="B21" s="116" t="s">
+      <c r="A21" s="123"/>
+      <c r="B21" s="115" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="118"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="117"/>
       <c r="E21" s="97"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="135"/>
-      <c r="B22" s="116" t="s">
+      <c r="A22" s="123"/>
+      <c r="B22" s="115" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="117"/>
       <c r="E22" s="97"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="136"/>
-      <c r="B23" s="122" t="s">
+      <c r="A23" s="124"/>
+      <c r="B23" s="118" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="123"/>
-      <c r="D23" s="124"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="120"/>
       <c r="E23" s="97" t="e">
         <f>((E20*(E12-E15))/E12)+E21*E13+E22</f>
         <v>#NUM!</v>
@@ -6113,36 +6142,36 @@
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="119" t="s">
+      <c r="A24" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="120"/>
-      <c r="C24" s="120"/>
-      <c r="D24" s="120"/>
-      <c r="E24" s="121"/>
+      <c r="B24" s="126"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="126"/>
+      <c r="E24" s="127"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="122" t="s">
+      <c r="A25" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="123"/>
-      <c r="C25" s="123"/>
-      <c r="D25" s="124"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="119"/>
+      <c r="D25" s="120"/>
       <c r="E25" s="97"/>
       <c r="F25" s="5"/>
       <c r="G25" s="70"/>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="125" t="s">
+      <c r="A26" s="128" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="126"/>
-      <c r="C26" s="126"/>
-      <c r="D26" s="127"/>
+      <c r="B26" s="129"/>
+      <c r="C26" s="129"/>
+      <c r="D26" s="130"/>
       <c r="E26" s="98" t="e">
         <f>E23-E25</f>
         <v>#NUM!</v>
@@ -6161,18 +6190,25 @@
       <c r="D36" s="79"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A24:E24"/>
+  <mergeCells count="45">
+    <mergeCell ref="S1:S3"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AH3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="M1:M3"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="P1:P3"/>
+    <mergeCell ref="Q1:Q3"/>
+    <mergeCell ref="R1:R3"/>
+    <mergeCell ref="O1:O3"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="I1:I3"/>
     <mergeCell ref="J1:J3"/>
@@ -6189,23 +6225,17 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="M1:M3"/>
-    <mergeCell ref="N1:N3"/>
-    <mergeCell ref="O1:O3"/>
-    <mergeCell ref="P1:P3"/>
-    <mergeCell ref="Q1:Q3"/>
-    <mergeCell ref="R1:R3"/>
-    <mergeCell ref="S1:W1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AF1"/>
-    <mergeCell ref="AG1:AG3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A24:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/public/payslip-template.xlsx
+++ b/public/payslip-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bin\JOB\THUCTAP\NHT\Payslip\Mẫu nhập\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C355FC4-E1C2-455D-95D4-DAE810B9D926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C5A7BF-6472-4342-BB9A-35D6F88EA188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{E78F4DFD-1167-45B0-99FC-E4DD07682841}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{E78F4DFD-1167-45B0-99FC-E4DD07682841}"/>
   </bookViews>
   <sheets>
     <sheet name="GV" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="124">
   <si>
     <t>Đơn vị:</t>
   </si>
@@ -403,6 +403,18 @@
   </si>
   <si>
     <t>Lương tháng 13</t>
+  </si>
+  <si>
+    <t>1.6.</t>
+  </si>
+  <si>
+    <t>MỨC LƯƠNG DẠY PHỤ ĐẠO KÈM</t>
+  </si>
+  <si>
+    <t>1.7.</t>
+  </si>
+  <si>
+    <t>LƯƠNG PLACEMENT TEST</t>
   </si>
 </sst>
 </file>
@@ -1211,9 +1223,6 @@
     <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1479,6 +1488,129 @@
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1488,6 +1620,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1497,6 +1638,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1509,23 +1674,98 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1535,234 +1775,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="31" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="36" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2037,6 +2049,60 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44B97C98-5280-4193-918F-FFB3DE55A841}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="9543" t="6729" r="11069" b="5238"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="95250" y="66675"/>
+          <a:ext cx="803088" cy="807547"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartConnector">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>898338</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>131272</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE72B1D1-D204-428D-B686-160B4C2935D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2485,921 +2551,961 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BDACFB-072F-4BA4-8D99-E94162A2FB42}">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" style="18" customWidth="1"/>
-    <col min="2" max="2" width="23.26953125" style="18" customWidth="1"/>
-    <col min="3" max="3" width="45.81640625" style="18" customWidth="1"/>
-    <col min="4" max="5" width="17.6328125" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.81640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" style="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.453125" style="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="18"/>
+    <col min="1" max="1" width="16.7265625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="45.81640625" style="17" customWidth="1"/>
+    <col min="4" max="5" width="17.6328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="19" t="s">
+      <c r="B1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="20"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="20"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B3" s="19"/>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="20"/>
+      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="20"/>
+      <c r="H4" s="19"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="H5" s="20"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="161" t="s">
+      <c r="A6" s="145" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="161"/>
-      <c r="C6" s="161"/>
-      <c r="D6" s="161"/>
-      <c r="E6" s="161"/>
-      <c r="F6" s="161"/>
-      <c r="G6" s="161"/>
-      <c r="H6" s="161"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="145"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="159"/>
-      <c r="C7" s="159"/>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="146"/>
+      <c r="G7" s="146"/>
+      <c r="H7" s="146"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="159"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="22" t="s">
+      <c r="B8" s="144"/>
+      <c r="C8" s="144"/>
+      <c r="D8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="159" t="s">
+      <c r="E8" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="159"/>
-      <c r="G8" s="159"/>
-      <c r="H8" s="159"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="159" t="s">
+      <c r="B9" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="159"/>
-      <c r="D9" s="22" t="s">
+      <c r="C9" s="144"/>
+      <c r="D9" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="159" t="s">
+      <c r="E9" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="159"/>
-      <c r="G9" s="159"/>
-      <c r="H9" s="159"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="159"/>
-      <c r="C10" s="159"/>
-      <c r="D10" s="22" t="s">
+      <c r="B10" s="144"/>
+      <c r="C10" s="144"/>
+      <c r="D10" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="159"/>
-      <c r="H10" s="159"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
     </row>
     <row r="11" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23">
+      <c r="A11" s="22">
         <v>1</v>
       </c>
-      <c r="B11" s="160" t="s">
+      <c r="B11" s="147" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="160"/>
-      <c r="D11" s="160"/>
-      <c r="E11" s="160"/>
-      <c r="F11" s="160"/>
-      <c r="G11" s="160"/>
-      <c r="H11" s="160"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="147"/>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="170" t="s">
+      <c r="B12" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="170"/>
-      <c r="D12" s="164"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="164"/>
-      <c r="G12" s="164"/>
-      <c r="H12" s="165"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="149"/>
+      <c r="H12" s="150"/>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="171" t="s">
+      <c r="B13" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="171"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="167"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="138"/>
+      <c r="G13" s="138"/>
+      <c r="H13" s="139"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="171" t="s">
+      <c r="B14" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="171"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="166"/>
-      <c r="F14" s="166"/>
-      <c r="G14" s="166"/>
-      <c r="H14" s="167"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="139"/>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="171" t="s">
+      <c r="B15" s="137" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="137"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="139"/>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="137" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="137"/>
+      <c r="D16" s="138">
+        <v>20000</v>
+      </c>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="139"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="137" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="171"/>
-      <c r="D15" s="166">
-        <v>0</v>
-      </c>
-      <c r="E15" s="166"/>
-      <c r="F15" s="166"/>
-      <c r="G15" s="166"/>
-      <c r="H15" s="167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="163" t="s">
+      <c r="C17" s="137"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="139"/>
+    </row>
+    <row r="18" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="163"/>
-      <c r="D16" s="168">
-        <v>0</v>
-      </c>
-      <c r="E16" s="168"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="168"/>
-      <c r="H16" s="169"/>
-    </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="24"/>
-    </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="23">
+      <c r="C18" s="148"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="151"/>
+      <c r="H18" s="152"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="23"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="22">
         <v>2</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="20"/>
-    </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="28" t="s">
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="20"/>
-    </row>
-    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="C21" s="28"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="19"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B22" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C22" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H22" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="58">
-        <f>G21*F21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="35"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="58">
-        <f t="shared" ref="H22:H30" si="0">G22*F22</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="34"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="11"/>
-      <c r="H23" s="58">
+      <c r="H23" s="57">
+        <f>G23*F23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="34"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="57">
+        <f t="shared" ref="H24:H32" si="0">G24*F24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="58">
+    <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="35"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="58">
-        <f>G25*F25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="30"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="58">
+    <row r="27" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="34"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="57">
+        <f>G27*F27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="41"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="58">
+    <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="40"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="41"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="58">
+    <row r="30" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="40"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="41"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="58">
+    <row r="31" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="41"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="58">
+    <row r="32" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="40"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="43"/>
-      <c r="B31" s="179" t="s">
+    <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="42"/>
+      <c r="B33" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="179"/>
-      <c r="D31" s="179"/>
-      <c r="E31" s="179"/>
-      <c r="F31" s="13">
-        <f>SUM(F21:F30)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="44"/>
-      <c r="H31" s="59">
-        <f>SUM(H21:H30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="28" t="s">
+      <c r="C33" s="133"/>
+      <c r="D33" s="133"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="13">
+        <f>SUM(F23:F32)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="43"/>
+      <c r="H33" s="58">
+        <f>SUM(H23:H32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B34" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="20"/>
-    </row>
-    <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="C34" s="28"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="19"/>
+    </row>
+    <row r="35" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B35" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C35" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D35" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E35" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F35" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G35" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="35"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
-    </row>
-    <row r="35" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="35"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12"/>
-    </row>
     <row r="36" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="14"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="16"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="33"/>
       <c r="G36" s="11"/>
       <c r="H36" s="12"/>
     </row>
-    <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="49"/>
+    <row r="37" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="34"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="33"/>
       <c r="G37" s="11"/>
-      <c r="H37" s="58">
-        <f t="shared" ref="H37" si="1">G37*F37</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="49"/>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="14"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="16"/>
       <c r="G38" s="11"/>
-      <c r="H38" s="58">
-        <f t="shared" ref="H38" si="2">G38*F38</f>
-        <v>0</v>
-      </c>
+      <c r="H38" s="12"/>
     </row>
     <row r="39" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="43"/>
-      <c r="B39" s="180" t="s">
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="57">
+        <f t="shared" ref="H39" si="1">G39*F39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="57">
+        <f t="shared" ref="H40" si="2">G40*F40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="42"/>
+      <c r="B41" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="181"/>
-      <c r="D39" s="181"/>
-      <c r="E39" s="181"/>
-      <c r="F39" s="16">
-        <f>SUM(F37:F38)</f>
-        <v>0</v>
-      </c>
-      <c r="G39" s="11"/>
-      <c r="H39" s="59">
-        <f>SUM(H37:H38)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="28" t="s">
+      <c r="C41" s="135"/>
+      <c r="D41" s="135"/>
+      <c r="E41" s="135"/>
+      <c r="F41" s="16">
+        <f>SUM(F39:F40)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="11"/>
+      <c r="H41" s="58">
+        <f>SUM(H39:H40)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B42" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="20"/>
-    </row>
-    <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="C42" s="28"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="19"/>
+    </row>
+    <row r="43" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B43" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D43" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E43" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F43" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G43" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="49"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="58">
-        <f>G42*F42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="58">
-        <f t="shared" ref="H43" si="3">G43*F43</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="44" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="180" t="s">
+      <c r="A44" s="29"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="57">
+        <f>G44*F44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="29"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="57">
+        <f t="shared" ref="H45" si="3">G45*F45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="181"/>
-      <c r="C44" s="181"/>
-      <c r="D44" s="181"/>
-      <c r="E44" s="182"/>
-      <c r="F44" s="16">
-        <f>SUM(F42:F43)</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="61"/>
-      <c r="H44" s="59">
-        <f>SUM(H42:H43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="28" t="s">
+      <c r="B46" s="135"/>
+      <c r="C46" s="135"/>
+      <c r="D46" s="135"/>
+      <c r="E46" s="136"/>
+      <c r="F46" s="16">
+        <f>SUM(F44:F45)</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="60"/>
+      <c r="H46" s="58">
+        <f>SUM(H44:H45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B47" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="20"/>
-    </row>
-    <row r="46" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="C47" s="28"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="19"/>
+    </row>
+    <row r="48" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B48" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D48" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E48" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F48" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G48" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H48" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="58">
-        <f>G47*F47</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="58">
-        <f t="shared" ref="H48" si="4">G48*F48</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="49" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="180" t="s">
+      <c r="A49" s="29"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="57">
+        <f>G49*F49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="29"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="57">
+        <f t="shared" ref="H50" si="4">G50*F50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="181"/>
-      <c r="C49" s="181"/>
-      <c r="D49" s="181"/>
-      <c r="E49" s="182"/>
-      <c r="F49" s="16">
-        <f>SUM(F47:F48)</f>
-        <v>0</v>
-      </c>
-      <c r="G49" s="61"/>
-      <c r="H49" s="59">
-        <f>SUM(H47:H48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="28" t="s">
+      <c r="B51" s="135"/>
+      <c r="C51" s="135"/>
+      <c r="D51" s="135"/>
+      <c r="E51" s="136"/>
+      <c r="F51" s="16">
+        <f>SUM(F49:F50)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="60"/>
+      <c r="H51" s="58">
+        <f>SUM(H49:H50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B52" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="20"/>
-    </row>
-    <row r="51" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="C52" s="28"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="19"/>
+    </row>
+    <row r="53" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B53" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C53" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D53" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="179" t="s">
+      <c r="E53" s="133"/>
+      <c r="F53" s="133"/>
+      <c r="G53" s="133"/>
+      <c r="H53" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="F51" s="179"/>
-      <c r="G51" s="179"/>
-      <c r="H51" s="50"/>
-    </row>
-    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="172" t="s">
+    </row>
+    <row r="54" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="140"/>
+      <c r="E54" s="141"/>
+      <c r="F54" s="141"/>
+      <c r="G54" s="142"/>
+      <c r="H54" s="49"/>
+    </row>
+    <row r="55" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="173"/>
-      <c r="C52" s="173"/>
-      <c r="D52" s="173"/>
-      <c r="E52" s="173"/>
-      <c r="F52" s="173"/>
-      <c r="G52" s="174"/>
-      <c r="H52" s="59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="28" t="s">
+      <c r="B55" s="141"/>
+      <c r="C55" s="141"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="141"/>
+      <c r="F55" s="141"/>
+      <c r="G55" s="142"/>
+      <c r="H55" s="58">
+        <f>SUM(H54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="175" t="s">
+      <c r="B56" s="143" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="175"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
-      <c r="H53" s="53"/>
-    </row>
-    <row r="54" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="176" t="s">
+      <c r="C56" s="143"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
+      <c r="G56" s="51"/>
+      <c r="H56" s="52"/>
+    </row>
+    <row r="57" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="177"/>
-      <c r="C54" s="177"/>
-      <c r="D54" s="177"/>
-      <c r="E54" s="178"/>
-      <c r="F54" s="184">
-        <v>0</v>
-      </c>
-      <c r="G54" s="185"/>
-      <c r="H54" s="186"/>
-    </row>
-    <row r="55" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="176" t="s">
+      <c r="B57" s="123"/>
+      <c r="C57" s="123"/>
+      <c r="D57" s="123"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="116">
+        <v>0</v>
+      </c>
+      <c r="G57" s="117"/>
+      <c r="H57" s="118"/>
+    </row>
+    <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="B55" s="177"/>
-      <c r="C55" s="177"/>
-      <c r="D55" s="177"/>
-      <c r="E55" s="178"/>
-      <c r="F55" s="184">
-        <v>0</v>
-      </c>
-      <c r="G55" s="185"/>
-      <c r="H55" s="186"/>
-    </row>
-    <row r="56" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="176" t="s">
+      <c r="B58" s="123"/>
+      <c r="C58" s="123"/>
+      <c r="D58" s="123"/>
+      <c r="E58" s="124"/>
+      <c r="F58" s="116">
+        <v>0</v>
+      </c>
+      <c r="G58" s="117"/>
+      <c r="H58" s="118"/>
+    </row>
+    <row r="59" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="177"/>
-      <c r="C56" s="177"/>
-      <c r="D56" s="177"/>
-      <c r="E56" s="178"/>
-      <c r="F56" s="184">
-        <v>0</v>
-      </c>
-      <c r="G56" s="185"/>
-      <c r="H56" s="186"/>
-    </row>
-    <row r="57" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="179" t="s">
+      <c r="B59" s="123"/>
+      <c r="C59" s="123"/>
+      <c r="D59" s="123"/>
+      <c r="E59" s="124"/>
+      <c r="F59" s="116">
+        <v>0</v>
+      </c>
+      <c r="G59" s="117"/>
+      <c r="H59" s="118"/>
+    </row>
+    <row r="60" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="133" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="179"/>
-      <c r="C57" s="179"/>
-      <c r="D57" s="179"/>
-      <c r="E57" s="179"/>
-      <c r="F57" s="187">
-        <f>F54+F55*F56</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="188"/>
-      <c r="H57" s="189"/>
-    </row>
-    <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="54"/>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="20"/>
-    </row>
-    <row r="59" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="55">
+      <c r="B60" s="133"/>
+      <c r="C60" s="133"/>
+      <c r="D60" s="133"/>
+      <c r="E60" s="133"/>
+      <c r="F60" s="119">
+        <f>F57+F58*F59</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="120"/>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="53"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="50"/>
+      <c r="D61" s="50"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
+      <c r="G61" s="51"/>
+      <c r="H61" s="19"/>
+    </row>
+    <row r="62" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="54">
         <v>3</v>
       </c>
-      <c r="B59" s="196" t="s">
+      <c r="B62" s="131" t="s">
         <v>68</v>
       </c>
-      <c r="C59" s="197"/>
-      <c r="D59" s="190"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="192"/>
-    </row>
-    <row r="60" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="190" t="s">
+      <c r="C62" s="132"/>
+      <c r="D62" s="125"/>
+      <c r="E62" s="126"/>
+      <c r="F62" s="126"/>
+      <c r="G62" s="126"/>
+      <c r="H62" s="127"/>
+    </row>
+    <row r="63" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="191"/>
-      <c r="C60" s="192"/>
-      <c r="D60" s="193"/>
-      <c r="E60" s="194"/>
-      <c r="F60" s="194"/>
-      <c r="G60" s="194"/>
-      <c r="H60" s="195"/>
-    </row>
-    <row r="61" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="56">
+      <c r="B63" s="126"/>
+      <c r="C63" s="127"/>
+      <c r="D63" s="128"/>
+      <c r="E63" s="129"/>
+      <c r="F63" s="129"/>
+      <c r="G63" s="129"/>
+      <c r="H63" s="130"/>
+    </row>
+    <row r="64" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="55">
         <v>4</v>
       </c>
-      <c r="B61" s="183" t="s">
+      <c r="B64" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="183"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="60">
-        <f>F57+H52+H49+H31+H39-D59</f>
+      <c r="C64" s="115"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="59">
+        <f>F60+H55+H51+H33+H41-D63+H46</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D16:H16"/>
+  <mergeCells count="45">
     <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D17:H17"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="E7:H7"/>
     <mergeCell ref="E8:H8"/>
     <mergeCell ref="E9:H9"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="D62:H62"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3411,332 +3517,326 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.36328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9" style="83"/>
-    <col min="4" max="4" width="6.7265625" style="83" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.54296875" style="99" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="83"/>
+    <col min="1" max="1" width="22.36328125" style="82" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9" style="82"/>
+    <col min="4" max="4" width="6.7265625" style="82" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.54296875" style="98" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="82"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="80"/>
-      <c r="B1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="81" t="s">
+      <c r="A1" s="79"/>
+      <c r="B1" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="80"/>
-      <c r="E1" s="82"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="81"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="82"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="81"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81" t="s">
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="80"/>
-      <c r="E3" s="82"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="81"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81" t="s">
+      <c r="A4" s="79"/>
+      <c r="B4" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="80"/>
-      <c r="E4" s="82"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="81"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="80"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="82"/>
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="81"/>
     </row>
     <row r="6" spans="1:8" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="135" t="s">
+      <c r="A6" s="154" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="135"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="154"/>
+      <c r="D6" s="154"/>
+      <c r="E6" s="154"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="86" t="s">
+      <c r="B7" s="167"/>
+      <c r="C7" s="168"/>
+      <c r="D7" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="E7" s="87"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="138" t="s">
+      <c r="B8" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="140"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="170"/>
+      <c r="E8" s="171"/>
+      <c r="F8" s="87"/>
+      <c r="G8" s="87"/>
+      <c r="H8" s="87"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="89"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="88"/>
+      <c r="A9" s="88"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
     </row>
     <row r="10" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="91"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
+      <c r="B10" s="156"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="157"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
     </row>
     <row r="11" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="115" t="s">
+      <c r="A11" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="87"/>
     </row>
     <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="115" t="s">
+      <c r="A12" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="92" t="e">
+      <c r="B12" s="156"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="157"/>
+      <c r="E12" s="91" t="e">
         <f>DAY(EOMONTH(DATE(E7,B7,1),0))</f>
         <v>#NUM!</v>
       </c>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="88"/>
+      <c r="F12" s="87"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="87"/>
     </row>
     <row r="13" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="155" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="88"/>
-      <c r="G13" s="88"/>
-      <c r="H13" s="88"/>
+      <c r="B13" s="156"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="157"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="115" t="s">
+      <c r="A14" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="116"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="88"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="157"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="87"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="87"/>
     </row>
     <row r="15" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="115" t="s">
+      <c r="A15" s="155" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="88"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="157"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="87"/>
     </row>
     <row r="16" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="115" t="s">
+      <c r="A16" s="155" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="116"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="88"/>
-      <c r="H16" s="88"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="115" t="s">
+      <c r="A17" s="155" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="116"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="93"/>
-      <c r="F17" s="88"/>
-      <c r="G17" s="88"/>
-      <c r="H17" s="88"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
     </row>
     <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="115" t="s">
+      <c r="A18" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="116"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="88"/>
-    </row>
-    <row r="19" spans="1:8" s="96" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="121" t="s">
+      <c r="B18" s="156"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+    </row>
+    <row r="19" spans="1:8" s="95" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="95"/>
-      <c r="G19" s="95"/>
-      <c r="H19" s="95"/>
+      <c r="B19" s="172"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="172"/>
+      <c r="E19" s="172"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="122" t="s">
+      <c r="A20" s="173" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="115" t="s">
+      <c r="B20" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="116"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="88"/>
-      <c r="G20" s="88"/>
-      <c r="H20" s="88"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="157"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="123"/>
-      <c r="B21" s="115" t="s">
+      <c r="A21" s="174"/>
+      <c r="B21" s="155" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="116"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="88"/>
-      <c r="G21" s="88"/>
-      <c r="H21" s="88"/>
+      <c r="C21" s="156"/>
+      <c r="D21" s="157"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="123"/>
-      <c r="B22" s="115" t="s">
+      <c r="A22" s="174"/>
+      <c r="B22" s="155" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="116"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="97"/>
-      <c r="F22" s="88"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="88"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="96"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="87"/>
     </row>
     <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="124"/>
-      <c r="B23" s="118" t="s">
+      <c r="A23" s="175"/>
+      <c r="B23" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="119"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="97" t="e">
+      <c r="C23" s="162"/>
+      <c r="D23" s="163"/>
+      <c r="E23" s="96" t="e">
         <f>((E20*(E12-E15))/E12)+E21*E13+E22</f>
         <v>#NUM!</v>
       </c>
-      <c r="F23" s="88"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
-    </row>
-    <row r="24" spans="1:8" s="96" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="125" t="s">
+      <c r="F23" s="87"/>
+      <c r="G23" s="87"/>
+      <c r="H23" s="87"/>
+    </row>
+    <row r="24" spans="1:8" s="95" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="158" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="126"/>
-      <c r="C24" s="126"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="95"/>
-      <c r="G24" s="95"/>
-      <c r="H24" s="95"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="159"/>
+      <c r="D24" s="159"/>
+      <c r="E24" s="160"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="94"/>
     </row>
     <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="118" t="s">
+      <c r="A25" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="119"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="120"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="88"/>
-      <c r="G25" s="88"/>
-      <c r="H25" s="88"/>
-    </row>
-    <row r="26" spans="1:8" s="96" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="128" t="s">
+      <c r="B25" s="162"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="163"/>
+      <c r="E25" s="96"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+    </row>
+    <row r="26" spans="1:8" s="95" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="129"/>
-      <c r="C26" s="129"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="98" t="e">
+      <c r="B26" s="165"/>
+      <c r="C26" s="165"/>
+      <c r="D26" s="166"/>
+      <c r="E26" s="97" t="e">
         <f>E23-E25</f>
         <v>#NUM!</v>
       </c>
-      <c r="F26" s="95"/>
-      <c r="G26" s="95"/>
-      <c r="H26" s="95"/>
+      <c r="F26" s="94"/>
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A26:D26"/>
@@ -3752,6 +3852,12 @@
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3765,7 +3871,7 @@
   <cols>
     <col min="1" max="1" width="28.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.08984375" style="72" customWidth="1"/>
+    <col min="5" max="5" width="39.08984375" style="71" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.54296875" bestFit="1" customWidth="1"/>
@@ -3781,7 +3887,7 @@
         <v>76</v>
       </c>
       <c r="D1" s="1"/>
-      <c r="E1" s="62"/>
+      <c r="E1" s="61"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
@@ -3792,7 +3898,7 @@
         <v>77</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="62"/>
+      <c r="E2" s="61"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
@@ -3803,34 +3909,34 @@
         <v>6</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="62"/>
+      <c r="E3" s="61"/>
     </row>
     <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="62"/>
+      <c r="E4" s="61"/>
     </row>
     <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.35">
-      <c r="A5" s="135" t="s">
+      <c r="A5" s="154" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135"/>
+      <c r="B5" s="154"/>
+      <c r="C5" s="154"/>
+      <c r="D5" s="154"/>
+      <c r="E5" s="154"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="205"/>
-      <c r="C6" s="205"/>
-      <c r="D6" s="63" t="s">
+      <c r="B6" s="180"/>
+      <c r="C6" s="180"/>
+      <c r="D6" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="65"/>
+      <c r="E6" s="64"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -3839,12 +3945,12 @@
       <c r="A7" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="206" t="s">
+      <c r="B7" s="181" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="206"/>
-      <c r="D7" s="206"/>
-      <c r="E7" s="206"/>
+      <c r="C7" s="181"/>
+      <c r="D7" s="181"/>
+      <c r="E7" s="181"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -3854,143 +3960,143 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="65"/>
+      <c r="E8" s="64"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="198" t="s">
+      <c r="A9" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="199"/>
-      <c r="C9" s="199"/>
-      <c r="D9" s="200"/>
+      <c r="B9" s="184"/>
+      <c r="C9" s="184"/>
+      <c r="D9" s="185"/>
       <c r="E9" s="7"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="198" t="s">
+      <c r="A10" s="183" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="199"/>
-      <c r="C10" s="199"/>
-      <c r="D10" s="200"/>
+      <c r="B10" s="184"/>
+      <c r="C10" s="184"/>
+      <c r="D10" s="185"/>
       <c r="E10" s="7"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-      <c r="J10" s="66"/>
-      <c r="K10" s="66"/>
-      <c r="L10" s="66"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
     </row>
     <row r="11" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="198" t="s">
+      <c r="A11" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="199"/>
-      <c r="C11" s="199"/>
-      <c r="D11" s="200"/>
+      <c r="B11" s="184"/>
+      <c r="C11" s="184"/>
+      <c r="D11" s="185"/>
       <c r="E11" s="7"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="66"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="67"/>
-      <c r="L11" s="67"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="66"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="66"/>
     </row>
     <row r="12" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="198" t="s">
+      <c r="A12" s="183" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="199"/>
-      <c r="C12" s="199"/>
-      <c r="D12" s="200"/>
-      <c r="E12" s="68"/>
+      <c r="B12" s="184"/>
+      <c r="C12" s="184"/>
+      <c r="D12" s="185"/>
+      <c r="E12" s="67"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="67"/>
-      <c r="L12" s="67"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="66"/>
     </row>
     <row r="13" spans="1:12" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="209" t="s">
+      <c r="A13" s="187" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="209"/>
-      <c r="C13" s="209"/>
-      <c r="D13" s="209"/>
-      <c r="E13" s="209"/>
+      <c r="B13" s="187"/>
+      <c r="C13" s="187"/>
+      <c r="D13" s="187"/>
+      <c r="E13" s="187"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="69"/>
-      <c r="L13" s="69"/>
+      <c r="J13" s="68"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="68"/>
     </row>
     <row r="14" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="207" t="s">
+      <c r="A14" s="182" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="201" t="s">
+      <c r="B14" s="176" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="73"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="176"/>
+      <c r="E14" s="72"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="67"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
     </row>
     <row r="15" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="207"/>
-      <c r="B15" s="201" t="s">
+      <c r="A15" s="182"/>
+      <c r="B15" s="176" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="201"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="74"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="176"/>
+      <c r="E15" s="73"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="69"/>
-      <c r="L15" s="69"/>
+      <c r="J15" s="68"/>
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
     </row>
     <row r="16" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="207"/>
-      <c r="B16" s="198" t="s">
+      <c r="A16" s="182"/>
+      <c r="B16" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="199"/>
-      <c r="D16" s="200"/>
-      <c r="E16" s="74"/>
+      <c r="C16" s="184"/>
+      <c r="D16" s="185"/>
+      <c r="E16" s="73"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="69"/>
-      <c r="L16" s="69"/>
+      <c r="J16" s="68"/>
+      <c r="K16" s="68"/>
+      <c r="L16" s="68"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="207"/>
-      <c r="B17" s="201" t="s">
+      <c r="A17" s="182"/>
+      <c r="B17" s="176" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="201"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="74">
+      <c r="C17" s="176"/>
+      <c r="D17" s="176"/>
+      <c r="E17" s="73">
         <f>SUM(E14:E16)</f>
         <v>0</v>
       </c>
@@ -3999,15 +4105,15 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="208" t="s">
+      <c r="A18" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="B18" s="201" t="s">
+      <c r="B18" s="176" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="201"/>
-      <c r="D18" s="201"/>
-      <c r="E18" s="74">
+      <c r="C18" s="176"/>
+      <c r="D18" s="176"/>
+      <c r="E18" s="73">
         <f>E14*8%</f>
         <v>0</v>
       </c>
@@ -4016,32 +4122,32 @@
       <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="208"/>
-      <c r="B19" s="201" t="s">
+      <c r="A19" s="186"/>
+      <c r="B19" s="176" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="201"/>
-      <c r="D19" s="201"/>
-      <c r="E19" s="74">
+      <c r="C19" s="176"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="73">
         <f>E14*1.5%</f>
         <v>0</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="67"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="66"/>
     </row>
     <row r="20" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="208"/>
-      <c r="B20" s="201" t="s">
+      <c r="A20" s="186"/>
+      <c r="B20" s="176" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="201"/>
-      <c r="D20" s="201"/>
-      <c r="E20" s="74">
+      <c r="C20" s="176"/>
+      <c r="D20" s="176"/>
+      <c r="E20" s="73">
         <f>E14*1%</f>
         <v>0</v>
       </c>
@@ -4050,25 +4156,25 @@
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="208"/>
-      <c r="B21" s="201" t="s">
+      <c r="A21" s="186"/>
+      <c r="B21" s="176" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="201"/>
-      <c r="D21" s="201"/>
-      <c r="E21" s="74"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="73"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="208"/>
-      <c r="B22" s="201" t="s">
+      <c r="A22" s="186"/>
+      <c r="B22" s="176" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="201"/>
-      <c r="D22" s="201"/>
-      <c r="E22" s="74">
+      <c r="C22" s="176"/>
+      <c r="D22" s="176"/>
+      <c r="E22" s="73">
         <f>SUM(E18:E21)</f>
         <v>0</v>
       </c>
@@ -4077,32 +4183,37 @@
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:12" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="202" t="s">
+      <c r="A23" s="177" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="203"/>
-      <c r="C23" s="203"/>
-      <c r="D23" s="204"/>
-      <c r="E23" s="75">
+      <c r="B23" s="178"/>
+      <c r="C23" s="178"/>
+      <c r="D23" s="179"/>
+      <c r="E23" s="74">
         <f>E17-E22</f>
         <v>0</v>
       </c>
       <c r="F23" s="5"/>
-      <c r="G23" s="70"/>
+      <c r="G23" s="69"/>
       <c r="H23" s="5"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="71" t="s">
+      <c r="A25" s="70" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="71" t="s">
+      <c r="A26" s="70" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="B6:C6"/>
@@ -4118,11 +4229,6 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -4132,1260 +4238,1304 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A81324B-B4FF-4119-98F2-558A38D65B72}">
-  <dimension ref="A1:AK61"/>
+  <dimension ref="A1:AK64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.54296875" style="83" customWidth="1"/>
-    <col min="2" max="2" width="18.08984375" style="83" customWidth="1"/>
-    <col min="3" max="3" width="33.90625" style="83" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.1796875" style="83" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.54296875" style="83" customWidth="1"/>
-    <col min="7" max="7" width="11.36328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.6328125" style="83" customWidth="1"/>
-    <col min="9" max="11" width="8.7265625" style="83"/>
-    <col min="12" max="12" width="6.7265625" style="83" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.54296875" style="83" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" style="83" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.453125" style="83" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.81640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.1796875" style="83" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.453125" style="83" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.36328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.26953125" style="83" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.90625" style="83" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.81640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.36328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.36328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.7265625" style="83" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.81640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.81640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="12.81640625" style="83" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.36328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.36328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.36328125" style="83" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.6328125" style="83" customWidth="1"/>
-    <col min="34" max="34" width="17.453125" style="83" customWidth="1"/>
-    <col min="35" max="35" width="16.81640625" style="83" customWidth="1"/>
-    <col min="36" max="36" width="9.6328125" style="83" customWidth="1"/>
-    <col min="37" max="16384" width="8.7265625" style="83"/>
+    <col min="1" max="1" width="16.7265625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" style="17" customWidth="1"/>
+    <col min="3" max="3" width="45.81640625" style="17" customWidth="1"/>
+    <col min="4" max="5" width="17.6328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.7265625" style="82"/>
+    <col min="12" max="12" width="6.7265625" style="82" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.54296875" style="82" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10" style="82" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.453125" style="82" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.81640625" style="82" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.1796875" style="82" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.453125" style="82" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.36328125" style="82" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.26953125" style="82" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.90625" style="82" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.81640625" style="82" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.36328125" style="82" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.36328125" style="82" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.7265625" style="82" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.81640625" style="82" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.81640625" style="82" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.81640625" style="82" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.36328125" style="82" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.36328125" style="82" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.36328125" style="82" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.6328125" style="82" customWidth="1"/>
+    <col min="34" max="34" width="17.453125" style="82" customWidth="1"/>
+    <col min="35" max="35" width="16.81640625" style="82" customWidth="1"/>
+    <col min="36" max="36" width="9.6328125" style="82" customWidth="1"/>
+    <col min="37" max="16384" width="8.7265625" style="82"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18"/>
-      <c r="B1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="19" t="s">
+      <c r="B1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="20"/>
-      <c r="L1" s="131" t="s">
+      <c r="H1" s="19"/>
+      <c r="L1" s="207" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="131" t="s">
+      <c r="M1" s="207" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="131" t="s">
+      <c r="N1" s="207" t="s">
         <v>91</v>
       </c>
-      <c r="O1" s="131" t="s">
+      <c r="O1" s="207" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="141" t="s">
+      <c r="P1" s="203" t="s">
         <v>93</v>
       </c>
-      <c r="Q1" s="144" t="s">
+      <c r="Q1" s="197" t="s">
         <v>94</v>
       </c>
-      <c r="R1" s="147" t="s">
+      <c r="R1" s="200" t="s">
         <v>119</v>
       </c>
-      <c r="S1" s="147" t="s">
+      <c r="S1" s="200" t="s">
         <v>95</v>
       </c>
-      <c r="T1" s="147" t="s">
+      <c r="T1" s="200" t="s">
         <v>96</v>
       </c>
-      <c r="U1" s="147" t="s">
+      <c r="U1" s="200" t="s">
         <v>97</v>
       </c>
-      <c r="V1" s="150" t="s">
+      <c r="V1" s="188" t="s">
         <v>98</v>
       </c>
-      <c r="W1" s="153" t="s">
+      <c r="W1" s="194" t="s">
         <v>99</v>
       </c>
-      <c r="X1" s="154"/>
-      <c r="Y1" s="154"/>
-      <c r="Z1" s="154"/>
-      <c r="AA1" s="155"/>
-      <c r="AB1" s="153" t="s">
+      <c r="X1" s="195"/>
+      <c r="Y1" s="195"/>
+      <c r="Z1" s="195"/>
+      <c r="AA1" s="196"/>
+      <c r="AB1" s="194" t="s">
         <v>100</v>
       </c>
-      <c r="AC1" s="155"/>
-      <c r="AD1" s="153" t="s">
+      <c r="AC1" s="196"/>
+      <c r="AD1" s="194" t="s">
         <v>101</v>
       </c>
-      <c r="AE1" s="154"/>
-      <c r="AF1" s="154"/>
-      <c r="AG1" s="154"/>
-      <c r="AH1" s="154"/>
-      <c r="AI1" s="154"/>
-      <c r="AJ1" s="154"/>
-      <c r="AK1" s="150" t="s">
+      <c r="AE1" s="195"/>
+      <c r="AF1" s="195"/>
+      <c r="AG1" s="195"/>
+      <c r="AH1" s="195"/>
+      <c r="AI1" s="195"/>
+      <c r="AJ1" s="195"/>
+      <c r="AK1" s="188" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="20"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="132"/>
-      <c r="P2" s="142"/>
-      <c r="Q2" s="145"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="148"/>
-      <c r="T2" s="148"/>
-      <c r="U2" s="148"/>
-      <c r="V2" s="151"/>
-      <c r="W2" s="100" t="s">
+      <c r="H2" s="19"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="208"/>
+      <c r="P2" s="204"/>
+      <c r="Q2" s="198"/>
+      <c r="R2" s="201"/>
+      <c r="S2" s="201"/>
+      <c r="T2" s="201"/>
+      <c r="U2" s="201"/>
+      <c r="V2" s="192"/>
+      <c r="W2" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="X2" s="100" t="s">
+      <c r="X2" s="99" t="s">
         <v>104</v>
       </c>
-      <c r="Y2" s="100" t="s">
+      <c r="Y2" s="99" t="s">
         <v>105</v>
       </c>
-      <c r="Z2" s="100" t="s">
+      <c r="Z2" s="99" t="s">
         <v>106</v>
       </c>
-      <c r="AA2" s="158" t="s">
+      <c r="AA2" s="191" t="s">
         <v>107</v>
       </c>
-      <c r="AB2" s="150" t="s">
+      <c r="AB2" s="188" t="s">
         <v>108</v>
       </c>
-      <c r="AC2" s="150" t="s">
+      <c r="AC2" s="188" t="s">
         <v>109</v>
       </c>
-      <c r="AD2" s="100" t="s">
+      <c r="AD2" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="AE2" s="100" t="s">
+      <c r="AE2" s="99" t="s">
         <v>104</v>
       </c>
-      <c r="AF2" s="100" t="s">
+      <c r="AF2" s="99" t="s">
         <v>105</v>
       </c>
-      <c r="AG2" s="150" t="s">
+      <c r="AG2" s="188" t="s">
         <v>110</v>
       </c>
-      <c r="AH2" s="150" t="s">
+      <c r="AH2" s="188" t="s">
         <v>111</v>
       </c>
-      <c r="AI2" s="150" t="s">
+      <c r="AI2" s="188" t="s">
         <v>112</v>
       </c>
-      <c r="AJ2" s="150" t="s">
+      <c r="AJ2" s="188" t="s">
         <v>113</v>
       </c>
-      <c r="AK2" s="156"/>
+      <c r="AK2" s="189"/>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="20"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="133"/>
-      <c r="N3" s="133"/>
-      <c r="O3" s="133"/>
-      <c r="P3" s="143"/>
-      <c r="Q3" s="146"/>
-      <c r="R3" s="149"/>
-      <c r="S3" s="149"/>
-      <c r="T3" s="149"/>
-      <c r="U3" s="149"/>
-      <c r="V3" s="152"/>
-      <c r="W3" s="101">
+      <c r="H3" s="19"/>
+      <c r="L3" s="209"/>
+      <c r="M3" s="209"/>
+      <c r="N3" s="209"/>
+      <c r="O3" s="209"/>
+      <c r="P3" s="205"/>
+      <c r="Q3" s="199"/>
+      <c r="R3" s="202"/>
+      <c r="S3" s="202"/>
+      <c r="T3" s="202"/>
+      <c r="U3" s="202"/>
+      <c r="V3" s="193"/>
+      <c r="W3" s="100">
         <v>0.17499999999999999</v>
       </c>
-      <c r="X3" s="101">
+      <c r="X3" s="100">
         <v>0.03</v>
       </c>
-      <c r="Y3" s="101">
+      <c r="Y3" s="100">
         <v>0.01</v>
       </c>
-      <c r="Z3" s="101">
+      <c r="Z3" s="100">
         <v>0.02</v>
       </c>
-      <c r="AA3" s="157"/>
-      <c r="AB3" s="157"/>
-      <c r="AC3" s="157"/>
-      <c r="AD3" s="101">
+      <c r="AA3" s="190"/>
+      <c r="AB3" s="190"/>
+      <c r="AC3" s="190"/>
+      <c r="AD3" s="100">
         <v>0.08</v>
       </c>
-      <c r="AE3" s="101">
+      <c r="AE3" s="100">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AF3" s="101">
+      <c r="AF3" s="100">
         <v>0.01</v>
       </c>
-      <c r="AG3" s="157"/>
-      <c r="AH3" s="157"/>
-      <c r="AI3" s="157"/>
-      <c r="AJ3" s="157"/>
-      <c r="AK3" s="157"/>
+      <c r="AG3" s="190"/>
+      <c r="AH3" s="190"/>
+      <c r="AI3" s="190"/>
+      <c r="AJ3" s="190"/>
+      <c r="AK3" s="190"/>
     </row>
     <row r="4" spans="1:37" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="20"/>
-      <c r="L4" s="104">
+      <c r="H4" s="19"/>
+      <c r="L4" s="103">
         <v>1</v>
       </c>
-      <c r="M4" s="105">
+      <c r="M4" s="104">
         <v>2</v>
       </c>
-      <c r="N4" s="105"/>
-      <c r="O4" s="104">
+      <c r="N4" s="104"/>
+      <c r="O4" s="103">
         <v>4</v>
       </c>
-      <c r="P4" s="104"/>
-      <c r="Q4" s="106"/>
-      <c r="R4" s="107"/>
-      <c r="S4" s="107"/>
-      <c r="T4" s="107"/>
-      <c r="U4" s="107"/>
-      <c r="V4" s="107">
+      <c r="P4" s="103"/>
+      <c r="Q4" s="105"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="106"/>
+      <c r="T4" s="106"/>
+      <c r="U4" s="106"/>
+      <c r="V4" s="106">
         <v>11</v>
       </c>
-      <c r="W4" s="107">
+      <c r="W4" s="106">
         <v>12</v>
       </c>
-      <c r="X4" s="107">
+      <c r="X4" s="106">
         <v>13</v>
       </c>
-      <c r="Y4" s="107">
+      <c r="Y4" s="106">
         <v>14</v>
       </c>
-      <c r="Z4" s="107">
+      <c r="Z4" s="106">
         <v>15</v>
       </c>
-      <c r="AA4" s="107">
+      <c r="AA4" s="106">
         <v>16</v>
       </c>
-      <c r="AB4" s="107">
+      <c r="AB4" s="106">
         <v>17</v>
       </c>
-      <c r="AC4" s="107">
+      <c r="AC4" s="106">
         <v>18</v>
       </c>
-      <c r="AD4" s="107">
+      <c r="AD4" s="106">
         <v>19</v>
       </c>
-      <c r="AE4" s="107">
+      <c r="AE4" s="106">
         <v>20</v>
       </c>
-      <c r="AF4" s="107">
+      <c r="AF4" s="106">
         <v>21</v>
       </c>
-      <c r="AG4" s="107">
+      <c r="AG4" s="106">
         <v>22</v>
       </c>
-      <c r="AH4" s="107">
+      <c r="AH4" s="106">
         <v>23</v>
       </c>
-      <c r="AI4" s="108">
+      <c r="AI4" s="107">
         <v>24</v>
       </c>
-      <c r="AJ4" s="107">
+      <c r="AJ4" s="106">
         <v>25</v>
       </c>
-      <c r="AK4" s="107">
+      <c r="AK4" s="106">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.35">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="20"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="110">
+      <c r="H5" s="19"/>
+      <c r="L5" s="101"/>
+      <c r="M5" s="108"/>
+      <c r="N5" s="108"/>
+      <c r="O5" s="109">
         <v>26</v>
       </c>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="111">
-        <v>0</v>
-      </c>
-      <c r="S5" s="111">
+      <c r="P5" s="110"/>
+      <c r="Q5" s="111"/>
+      <c r="R5" s="110">
+        <v>0</v>
+      </c>
+      <c r="S5" s="110">
         <f>((P5/O5)*O5)+SUM(Q5:R5)</f>
         <v>0</v>
       </c>
-      <c r="T5" s="111">
+      <c r="T5" s="110">
         <f>S5-Q5</f>
         <v>0</v>
       </c>
-      <c r="U5" s="111">
-        <v>0</v>
-      </c>
-      <c r="V5" s="111">
+      <c r="U5" s="110">
+        <v>0</v>
+      </c>
+      <c r="V5" s="110">
         <f>P5</f>
         <v>0</v>
       </c>
-      <c r="W5" s="103">
+      <c r="W5" s="102">
         <f>V5*W3</f>
         <v>0</v>
       </c>
-      <c r="X5" s="103">
+      <c r="X5" s="102">
         <f>V5*X3</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="103">
+      <c r="Y5" s="102">
         <f>V5*Y3</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="103">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="103">
+      <c r="Z5" s="102">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="102">
         <f>SUM(W5:Y5)</f>
         <v>0</v>
       </c>
-      <c r="AB5" s="103"/>
-      <c r="AC5" s="103">
+      <c r="AB5" s="102"/>
+      <c r="AC5" s="102">
         <v>15500000</v>
       </c>
-      <c r="AD5" s="103">
+      <c r="AD5" s="102">
         <f>V5*AD3</f>
         <v>0</v>
       </c>
-      <c r="AE5" s="103">
+      <c r="AE5" s="102">
         <f>V5*AE3</f>
         <v>0</v>
       </c>
-      <c r="AF5" s="103">
+      <c r="AF5" s="102">
         <f>V5*AF3</f>
         <v>0</v>
       </c>
-      <c r="AG5" s="103">
+      <c r="AG5" s="102">
         <f>SUM(AD5:AF5)</f>
         <v>0</v>
       </c>
-      <c r="AH5" s="103">
+      <c r="AH5" s="102">
         <f>MAX(T5-AB5-AC5-AG5,0)</f>
         <v>0</v>
       </c>
-      <c r="AI5" s="103">
+      <c r="AI5" s="102">
         <f>MIN(AH5,10000000)*0.05+MAX(MIN(AH5-10000000,20000000),0)*0.1+MAX(MIN(AH5-30000000,30000000),0)*0.2+MAX(MIN(AH5-60000000,40000000),0)*0.3+MAX(AH5-100000000,0)*0.35</f>
         <v>0</v>
       </c>
-      <c r="AJ5" s="103">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="103">
+      <c r="AJ5" s="102">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="102">
         <f>S5+U5-AG5-AI5-AJ5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:37" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="161" t="s">
+      <c r="A6" s="145" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="161"/>
-      <c r="C6" s="161"/>
-      <c r="D6" s="161"/>
-      <c r="E6" s="161"/>
-      <c r="F6" s="161"/>
-      <c r="G6" s="161"/>
-      <c r="H6" s="161"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="145"/>
+      <c r="H6" s="145"/>
     </row>
     <row r="7" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="159"/>
-      <c r="C7" s="159"/>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="144"/>
+      <c r="C7" s="144"/>
+      <c r="D7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
-      <c r="O7" s="134" t="s">
+      <c r="E7" s="146"/>
+      <c r="F7" s="146"/>
+      <c r="G7" s="146"/>
+      <c r="H7" s="146"/>
+      <c r="O7" s="206" t="s">
         <v>114</v>
       </c>
-      <c r="P7" s="134"/>
-      <c r="Q7" s="114">
+      <c r="P7" s="206"/>
+      <c r="Q7" s="113">
         <f>AK5</f>
         <v>0</v>
       </c>
-      <c r="R7" s="113"/>
+      <c r="R7" s="112"/>
     </row>
     <row r="8" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="159"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="22" t="s">
+      <c r="B8" s="144"/>
+      <c r="C8" s="144"/>
+      <c r="D8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="159" t="s">
+      <c r="E8" s="144" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="159"/>
-      <c r="G8" s="159"/>
-      <c r="H8" s="159"/>
-      <c r="O8" s="134" t="s">
+      <c r="F8" s="144"/>
+      <c r="G8" s="144"/>
+      <c r="H8" s="144"/>
+      <c r="O8" s="206" t="s">
         <v>115</v>
       </c>
-      <c r="P8" s="134"/>
-      <c r="Q8" s="114">
-        <f>H61-Q7</f>
+      <c r="P8" s="206"/>
+      <c r="Q8" s="113">
+        <f>H64-Q7</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="159" t="s">
+      <c r="B9" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="159"/>
-      <c r="D9" s="22" t="s">
+      <c r="C9" s="144"/>
+      <c r="D9" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="159" t="s">
+      <c r="E9" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="159"/>
-      <c r="G9" s="159"/>
-      <c r="H9" s="159"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="144"/>
+      <c r="H9" s="144"/>
     </row>
     <row r="10" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="159"/>
-      <c r="C10" s="159"/>
-      <c r="D10" s="22" t="s">
+      <c r="B10" s="144"/>
+      <c r="C10" s="144"/>
+      <c r="D10" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="159"/>
-      <c r="H10" s="159"/>
+      <c r="E10" s="144"/>
+      <c r="F10" s="144"/>
+      <c r="G10" s="144"/>
+      <c r="H10" s="144"/>
     </row>
     <row r="11" spans="1:37" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23">
+      <c r="A11" s="22">
         <v>1</v>
       </c>
-      <c r="B11" s="160" t="s">
+      <c r="B11" s="147" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="160"/>
-      <c r="D11" s="160"/>
-      <c r="E11" s="160"/>
-      <c r="F11" s="160"/>
-      <c r="G11" s="160"/>
-      <c r="H11" s="160"/>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="147"/>
+      <c r="G11" s="147"/>
+      <c r="H11" s="147"/>
     </row>
     <row r="12" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="170" t="s">
+      <c r="B12" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="170"/>
-      <c r="D12" s="164"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="164"/>
-      <c r="G12" s="164"/>
-      <c r="H12" s="165"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="149"/>
+      <c r="H12" s="150"/>
     </row>
     <row r="13" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="171" t="s">
+      <c r="B13" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="171"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="167"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="138"/>
+      <c r="E13" s="138"/>
+      <c r="F13" s="138"/>
+      <c r="G13" s="138"/>
+      <c r="H13" s="139"/>
     </row>
     <row r="14" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="171" t="s">
+      <c r="B14" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="171"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="166"/>
-      <c r="F14" s="166"/>
-      <c r="G14" s="166"/>
-      <c r="H14" s="167"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="139"/>
     </row>
     <row r="15" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="171" t="s">
+      <c r="B15" s="137" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="137"/>
+      <c r="D15" s="138"/>
+      <c r="E15" s="138"/>
+      <c r="F15" s="138"/>
+      <c r="G15" s="138"/>
+      <c r="H15" s="139"/>
+    </row>
+    <row r="16" spans="1:37" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="137" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="137"/>
+      <c r="D16" s="138">
+        <v>20000</v>
+      </c>
+      <c r="E16" s="138"/>
+      <c r="F16" s="138"/>
+      <c r="G16" s="138"/>
+      <c r="H16" s="139"/>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="137" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="171"/>
-      <c r="D15" s="166">
-        <v>0</v>
-      </c>
-      <c r="E15" s="166"/>
-      <c r="F15" s="166"/>
-      <c r="G15" s="166"/>
-      <c r="H15" s="167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="163" t="s">
+      <c r="C17" s="137"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="139"/>
+    </row>
+    <row r="18" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="163"/>
-      <c r="D16" s="168">
-        <v>0</v>
-      </c>
-      <c r="E16" s="168"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="168"/>
-      <c r="H16" s="169"/>
-    </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="24"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-    </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="23">
+      <c r="C18" s="148"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="151"/>
+      <c r="H18" s="152"/>
+    </row>
+    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="23"/>
+    </row>
+    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="22">
         <v>2</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="20"/>
-    </row>
-    <row r="19" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="28" t="s">
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="20"/>
-    </row>
-    <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
+      <c r="C21" s="28"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="19"/>
+    </row>
+    <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B22" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C22" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D22" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H22" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="58">
-        <f>G21*F21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="35"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="58">
-        <f t="shared" ref="H22:H30" si="0">G22*F22</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="23" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="30"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="34"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
       <c r="G23" s="11"/>
-      <c r="H23" s="58">
+      <c r="H23" s="57">
+        <f>G23*F23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="34"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="57">
+        <f t="shared" ref="H24:H32" si="0">G24*F24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="29"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="30"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="58">
+    <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="35"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="58">
-        <f>G25*F25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="30"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="58">
+    <row r="27" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="34"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="57">
+        <f>G27*F27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="41"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="58">
+    <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="40"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="41"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="58">
+    <row r="30" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="40"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="41"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="58">
+    <row r="31" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="41"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="58">
+    <row r="32" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="40"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="57">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="43"/>
-      <c r="B31" s="179" t="s">
+    <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="42"/>
+      <c r="B33" s="133" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="179"/>
-      <c r="D31" s="179"/>
-      <c r="E31" s="179"/>
-      <c r="F31" s="13">
-        <f>SUM(F21:F30)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="44"/>
-      <c r="H31" s="59">
-        <f>SUM(H21:H30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="28" t="s">
+      <c r="C33" s="133"/>
+      <c r="D33" s="133"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="13">
+        <f>SUM(F23:F32)</f>
+        <v>0</v>
+      </c>
+      <c r="G33" s="43"/>
+      <c r="H33" s="58">
+        <f>SUM(H23:H32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B34" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="20"/>
-    </row>
-    <row r="33" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
+      <c r="C34" s="28"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="19"/>
+    </row>
+    <row r="35" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B35" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C35" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D35" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E35" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F35" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G35" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H35" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="35"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
-    </row>
-    <row r="35" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="35"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12"/>
-    </row>
     <row r="36" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="14"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-      <c r="F36" s="16"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="33"/>
       <c r="G36" s="11"/>
       <c r="H36" s="12"/>
     </row>
     <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="30"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="49"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="33"/>
       <c r="G37" s="11"/>
-      <c r="H37" s="58">
-        <f t="shared" ref="H37:H38" si="1">G37*F37</f>
-        <v>0</v>
-      </c>
+      <c r="H37" s="12"/>
     </row>
     <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="30"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="49"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="16"/>
       <c r="G38" s="11"/>
-      <c r="H38" s="58">
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="29"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="57">
+        <f t="shared" ref="H39:H40" si="1">G39*F39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="57">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="43"/>
-      <c r="B39" s="180" t="s">
+    <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="42"/>
+      <c r="B41" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="C39" s="181"/>
-      <c r="D39" s="181"/>
-      <c r="E39" s="181"/>
-      <c r="F39" s="16">
-        <f>SUM(F37:F38)</f>
-        <v>0</v>
-      </c>
-      <c r="G39" s="11"/>
-      <c r="H39" s="59">
-        <f>SUM(H37:H38)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="28" t="s">
+      <c r="C41" s="135"/>
+      <c r="D41" s="135"/>
+      <c r="E41" s="135"/>
+      <c r="F41" s="16">
+        <f>SUM(F39:F40)</f>
+        <v>0</v>
+      </c>
+      <c r="G41" s="11"/>
+      <c r="H41" s="58">
+        <f>SUM(H39:H40)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B42" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="20"/>
-    </row>
-    <row r="41" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
+      <c r="C42" s="28"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="19"/>
+    </row>
+    <row r="43" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B43" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C43" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D43" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E43" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F43" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G43" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H43" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="49"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="58">
-        <f>G42*F42</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="30"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="49"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="58">
-        <f t="shared" ref="H43" si="2">G43*F43</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="44" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="180" t="s">
+      <c r="A44" s="29"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="57">
+        <f>G44*F44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="29"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="57">
+        <f t="shared" ref="H45" si="2">G45*F45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="181"/>
-      <c r="C44" s="181"/>
-      <c r="D44" s="181"/>
-      <c r="E44" s="182"/>
-      <c r="F44" s="16">
-        <f>SUM(F42:F43)</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="61"/>
-      <c r="H44" s="59">
-        <f>SUM(H42:H43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="28" t="s">
+      <c r="B46" s="135"/>
+      <c r="C46" s="135"/>
+      <c r="D46" s="135"/>
+      <c r="E46" s="136"/>
+      <c r="F46" s="16">
+        <f>SUM(F44:F45)</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="60"/>
+      <c r="H46" s="58">
+        <f>SUM(H44:H45)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B47" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="20"/>
-    </row>
-    <row r="46" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
+      <c r="C47" s="28"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="19"/>
+    </row>
+    <row r="48" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B48" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C48" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D48" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E48" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F46" s="8" t="s">
+      <c r="F48" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G48" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H48" s="10" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="58">
-        <f>G47*F47</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="49"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="58">
-        <f t="shared" ref="H48" si="3">G48*F48</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="49" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="180" t="s">
+      <c r="A49" s="29"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="57">
+        <f>G49*F49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="29"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="57">
+        <f t="shared" ref="H50" si="3">G50*F50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="134" t="s">
         <v>58</v>
       </c>
-      <c r="B49" s="181"/>
-      <c r="C49" s="181"/>
-      <c r="D49" s="181"/>
-      <c r="E49" s="182"/>
-      <c r="F49" s="16">
-        <f>SUM(F47:F48)</f>
-        <v>0</v>
-      </c>
-      <c r="G49" s="61"/>
-      <c r="H49" s="59">
-        <f>SUM(H47:H48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="28" t="s">
+      <c r="B51" s="135"/>
+      <c r="C51" s="135"/>
+      <c r="D51" s="135"/>
+      <c r="E51" s="136"/>
+      <c r="F51" s="16">
+        <f>SUM(F49:F50)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="60"/>
+      <c r="H51" s="58">
+        <f>SUM(H49:H50)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B52" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="20"/>
-    </row>
-    <row r="51" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
+      <c r="C52" s="28"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="19"/>
+    </row>
+    <row r="53" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B53" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C53" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D53" s="133" t="s">
         <v>63</v>
       </c>
-      <c r="E51" s="179" t="s">
+      <c r="E53" s="133"/>
+      <c r="F53" s="133"/>
+      <c r="G53" s="133"/>
+      <c r="H53" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="F51" s="179"/>
-      <c r="G51" s="179"/>
-      <c r="H51" s="50"/>
-    </row>
-    <row r="52" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="172" t="s">
+    </row>
+    <row r="54" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="140"/>
+      <c r="E54" s="141"/>
+      <c r="F54" s="141"/>
+      <c r="G54" s="142"/>
+      <c r="H54" s="49"/>
+    </row>
+    <row r="55" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="173"/>
-      <c r="C52" s="173"/>
-      <c r="D52" s="173"/>
-      <c r="E52" s="173"/>
-      <c r="F52" s="173"/>
-      <c r="G52" s="174"/>
-      <c r="H52" s="59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="28" t="s">
+      <c r="B55" s="141"/>
+      <c r="C55" s="141"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="141"/>
+      <c r="F55" s="141"/>
+      <c r="G55" s="142"/>
+      <c r="H55" s="58">
+        <f>SUM(H54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="175" t="s">
+      <c r="B56" s="143" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="175"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="52"/>
-      <c r="H53" s="53"/>
-    </row>
-    <row r="54" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="176" t="s">
+      <c r="C56" s="143"/>
+      <c r="D56" s="50"/>
+      <c r="E56" s="51"/>
+      <c r="F56" s="51"/>
+      <c r="G56" s="51"/>
+      <c r="H56" s="52"/>
+    </row>
+    <row r="57" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="B54" s="177"/>
-      <c r="C54" s="177"/>
-      <c r="D54" s="177"/>
-      <c r="E54" s="178"/>
-      <c r="F54" s="184">
-        <v>0</v>
-      </c>
-      <c r="G54" s="185"/>
-      <c r="H54" s="186"/>
-    </row>
-    <row r="55" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="176" t="s">
+      <c r="B57" s="123"/>
+      <c r="C57" s="123"/>
+      <c r="D57" s="123"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="116">
+        <v>0</v>
+      </c>
+      <c r="G57" s="117"/>
+      <c r="H57" s="118"/>
+    </row>
+    <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="B55" s="177"/>
-      <c r="C55" s="177"/>
-      <c r="D55" s="177"/>
-      <c r="E55" s="178"/>
-      <c r="F55" s="184">
-        <v>0</v>
-      </c>
-      <c r="G55" s="185"/>
-      <c r="H55" s="186"/>
-    </row>
-    <row r="56" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="176" t="s">
+      <c r="B58" s="123"/>
+      <c r="C58" s="123"/>
+      <c r="D58" s="123"/>
+      <c r="E58" s="124"/>
+      <c r="F58" s="116">
+        <v>0</v>
+      </c>
+      <c r="G58" s="117"/>
+      <c r="H58" s="118"/>
+    </row>
+    <row r="59" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="B56" s="177"/>
-      <c r="C56" s="177"/>
-      <c r="D56" s="177"/>
-      <c r="E56" s="178"/>
-      <c r="F56" s="184">
-        <v>0</v>
-      </c>
-      <c r="G56" s="185"/>
-      <c r="H56" s="186"/>
-    </row>
-    <row r="57" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="179" t="s">
+      <c r="B59" s="123"/>
+      <c r="C59" s="123"/>
+      <c r="D59" s="123"/>
+      <c r="E59" s="124"/>
+      <c r="F59" s="116">
+        <v>0</v>
+      </c>
+      <c r="G59" s="117"/>
+      <c r="H59" s="118"/>
+    </row>
+    <row r="60" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="133" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="179"/>
-      <c r="C57" s="179"/>
-      <c r="D57" s="179"/>
-      <c r="E57" s="179"/>
-      <c r="F57" s="187">
-        <f>F54+F55*F56</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="188"/>
-      <c r="H57" s="189"/>
-    </row>
-    <row r="58" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="54"/>
-      <c r="B58" s="51"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="52"/>
-      <c r="H58" s="20"/>
-    </row>
-    <row r="59" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="55">
+      <c r="B60" s="133"/>
+      <c r="C60" s="133"/>
+      <c r="D60" s="133"/>
+      <c r="E60" s="133"/>
+      <c r="F60" s="119">
+        <f>F57+F58*F59</f>
+        <v>0</v>
+      </c>
+      <c r="G60" s="120"/>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="53"/>
+      <c r="B61" s="50"/>
+      <c r="C61" s="50"/>
+      <c r="D61" s="50"/>
+      <c r="E61" s="50"/>
+      <c r="F61" s="51"/>
+      <c r="G61" s="51"/>
+      <c r="H61" s="19"/>
+    </row>
+    <row r="62" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="54">
         <v>3</v>
       </c>
-      <c r="B59" s="196" t="s">
+      <c r="B62" s="131" t="s">
         <v>68</v>
       </c>
-      <c r="C59" s="197"/>
-      <c r="D59" s="190"/>
-      <c r="E59" s="191"/>
-      <c r="F59" s="191"/>
-      <c r="G59" s="191"/>
-      <c r="H59" s="192"/>
-    </row>
-    <row r="60" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="190" t="s">
+      <c r="C62" s="132"/>
+      <c r="D62" s="125"/>
+      <c r="E62" s="126"/>
+      <c r="F62" s="126"/>
+      <c r="G62" s="126"/>
+      <c r="H62" s="127"/>
+    </row>
+    <row r="63" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="B60" s="191"/>
-      <c r="C60" s="192"/>
-      <c r="D60" s="193"/>
-      <c r="E60" s="194"/>
-      <c r="F60" s="194"/>
-      <c r="G60" s="194"/>
-      <c r="H60" s="195"/>
-    </row>
-    <row r="61" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="56">
+      <c r="B63" s="126"/>
+      <c r="C63" s="127"/>
+      <c r="D63" s="128"/>
+      <c r="E63" s="129"/>
+      <c r="F63" s="129"/>
+      <c r="G63" s="129"/>
+      <c r="H63" s="130"/>
+    </row>
+    <row r="64" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="55">
         <v>4</v>
       </c>
-      <c r="B61" s="183" t="s">
+      <c r="B64" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="C61" s="183"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="60">
-        <f>F57+H52+H49+H31+H39-D59</f>
+      <c r="C64" s="115"/>
+      <c r="D64" s="56"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="56"/>
+      <c r="G64" s="56"/>
+      <c r="H64" s="59">
+        <f>F60+H55+H51+H33+H41-D63+H46</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="AK1:AK3"/>
-    <mergeCell ref="AC2:AC3"/>
-    <mergeCell ref="AJ2:AJ3"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="AH2:AH3"/>
-    <mergeCell ref="AI2:AI3"/>
+  <mergeCells count="69">
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="F58:H58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="F59:H59"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:H62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="D63:H63"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D53:G53"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="E10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="P1:P3"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="L1:L3"/>
+    <mergeCell ref="M1:M3"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="O1:O3"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:H16"/>
     <mergeCell ref="V1:V3"/>
     <mergeCell ref="W1:AA1"/>
     <mergeCell ref="AB1:AC1"/>
@@ -5395,53 +5545,14 @@
     <mergeCell ref="S1:S3"/>
     <mergeCell ref="T1:T3"/>
     <mergeCell ref="U1:U3"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="L1:L3"/>
-    <mergeCell ref="M1:M3"/>
-    <mergeCell ref="N1:N3"/>
-    <mergeCell ref="O1:O3"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="D60:H60"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="P1:P3"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="F55:H55"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="E10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="AC2:AC3"/>
+    <mergeCell ref="AJ2:AJ3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AB3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="AH2:AH3"/>
+    <mergeCell ref="AI2:AI3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B8" xr:uid="{82479240-5D3B-410A-AD98-6642A9B2C328}">
@@ -5460,7 +5571,7 @@
   <cols>
     <col min="1" max="1" width="17.08984375" customWidth="1"/>
     <col min="4" max="4" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="57.81640625" style="72" customWidth="1"/>
+    <col min="5" max="5" width="57.81640625" style="71" customWidth="1"/>
     <col min="9" max="9" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
@@ -5488,515 +5599,515 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A1" s="80"/>
-      <c r="B1" s="81" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="81" t="s">
+      <c r="A1" s="79"/>
+      <c r="B1" s="80" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="80"/>
-      <c r="E1" s="82"/>
-      <c r="I1" s="131" t="s">
+      <c r="D1" s="79"/>
+      <c r="E1" s="81"/>
+      <c r="I1" s="207" t="s">
         <v>89</v>
       </c>
-      <c r="J1" s="131" t="s">
+      <c r="J1" s="207" t="s">
         <v>90</v>
       </c>
-      <c r="K1" s="131" t="s">
+      <c r="K1" s="207" t="s">
         <v>91</v>
       </c>
-      <c r="L1" s="131" t="s">
+      <c r="L1" s="207" t="s">
         <v>92</v>
       </c>
-      <c r="M1" s="141" t="s">
+      <c r="M1" s="203" t="s">
         <v>93</v>
       </c>
-      <c r="N1" s="144" t="s">
+      <c r="N1" s="197" t="s">
         <v>94</v>
       </c>
-      <c r="O1" s="147" t="s">
+      <c r="O1" s="200" t="s">
         <v>119</v>
       </c>
-      <c r="P1" s="147" t="s">
+      <c r="P1" s="200" t="s">
         <v>95</v>
       </c>
-      <c r="Q1" s="147" t="s">
+      <c r="Q1" s="200" t="s">
         <v>96</v>
       </c>
-      <c r="R1" s="147" t="s">
+      <c r="R1" s="200" t="s">
         <v>97</v>
       </c>
-      <c r="S1" s="150" t="s">
+      <c r="S1" s="188" t="s">
         <v>98</v>
       </c>
-      <c r="T1" s="153" t="s">
+      <c r="T1" s="194" t="s">
         <v>99</v>
       </c>
-      <c r="U1" s="154"/>
-      <c r="V1" s="154"/>
-      <c r="W1" s="154"/>
-      <c r="X1" s="155"/>
-      <c r="Y1" s="153" t="s">
+      <c r="U1" s="195"/>
+      <c r="V1" s="195"/>
+      <c r="W1" s="195"/>
+      <c r="X1" s="196"/>
+      <c r="Y1" s="194" t="s">
         <v>100</v>
       </c>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="153" t="s">
+      <c r="Z1" s="196"/>
+      <c r="AA1" s="194" t="s">
         <v>101</v>
       </c>
-      <c r="AB1" s="154"/>
-      <c r="AC1" s="154"/>
-      <c r="AD1" s="154"/>
-      <c r="AE1" s="154"/>
-      <c r="AF1" s="154"/>
-      <c r="AG1" s="154"/>
-      <c r="AH1" s="150" t="s">
+      <c r="AB1" s="195"/>
+      <c r="AC1" s="195"/>
+      <c r="AD1" s="195"/>
+      <c r="AE1" s="195"/>
+      <c r="AF1" s="195"/>
+      <c r="AG1" s="195"/>
+      <c r="AH1" s="188" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="82"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="142"/>
-      <c r="N2" s="145"/>
-      <c r="O2" s="148"/>
-      <c r="P2" s="148"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="151"/>
-      <c r="T2" s="100" t="s">
+      <c r="D2" s="79"/>
+      <c r="E2" s="81"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="204"/>
+      <c r="N2" s="198"/>
+      <c r="O2" s="201"/>
+      <c r="P2" s="201"/>
+      <c r="Q2" s="201"/>
+      <c r="R2" s="201"/>
+      <c r="S2" s="192"/>
+      <c r="T2" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="U2" s="100" t="s">
+      <c r="U2" s="99" t="s">
         <v>104</v>
       </c>
-      <c r="V2" s="100" t="s">
+      <c r="V2" s="99" t="s">
         <v>105</v>
       </c>
-      <c r="W2" s="100" t="s">
+      <c r="W2" s="99" t="s">
         <v>106</v>
       </c>
-      <c r="X2" s="158" t="s">
+      <c r="X2" s="191" t="s">
         <v>107</v>
       </c>
-      <c r="Y2" s="150" t="s">
+      <c r="Y2" s="188" t="s">
         <v>108</v>
       </c>
-      <c r="Z2" s="150" t="s">
+      <c r="Z2" s="188" t="s">
         <v>109</v>
       </c>
-      <c r="AA2" s="100" t="s">
+      <c r="AA2" s="99" t="s">
         <v>103</v>
       </c>
-      <c r="AB2" s="100" t="s">
+      <c r="AB2" s="99" t="s">
         <v>104</v>
       </c>
-      <c r="AC2" s="100" t="s">
+      <c r="AC2" s="99" t="s">
         <v>105</v>
       </c>
-      <c r="AD2" s="150" t="s">
+      <c r="AD2" s="188" t="s">
         <v>110</v>
       </c>
-      <c r="AE2" s="150" t="s">
+      <c r="AE2" s="188" t="s">
         <v>111</v>
       </c>
-      <c r="AF2" s="150" t="s">
+      <c r="AF2" s="188" t="s">
         <v>112</v>
       </c>
-      <c r="AG2" s="150" t="s">
+      <c r="AG2" s="188" t="s">
         <v>113</v>
       </c>
-      <c r="AH2" s="156"/>
+      <c r="AH2" s="189"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81" t="s">
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="80"/>
-      <c r="E3" s="82"/>
-      <c r="I3" s="133"/>
-      <c r="J3" s="133"/>
-      <c r="K3" s="133"/>
-      <c r="L3" s="133"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="146"/>
-      <c r="O3" s="149"/>
-      <c r="P3" s="149"/>
-      <c r="Q3" s="149"/>
-      <c r="R3" s="149"/>
-      <c r="S3" s="152"/>
-      <c r="T3" s="101">
+      <c r="D3" s="79"/>
+      <c r="E3" s="81"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="209"/>
+      <c r="K3" s="209"/>
+      <c r="L3" s="209"/>
+      <c r="M3" s="205"/>
+      <c r="N3" s="199"/>
+      <c r="O3" s="202"/>
+      <c r="P3" s="202"/>
+      <c r="Q3" s="202"/>
+      <c r="R3" s="202"/>
+      <c r="S3" s="193"/>
+      <c r="T3" s="100">
         <v>0.17499999999999999</v>
       </c>
-      <c r="U3" s="101">
+      <c r="U3" s="100">
         <v>0.03</v>
       </c>
-      <c r="V3" s="101">
+      <c r="V3" s="100">
         <v>0.01</v>
       </c>
-      <c r="W3" s="101">
+      <c r="W3" s="100">
         <v>0.02</v>
       </c>
-      <c r="X3" s="157"/>
-      <c r="Y3" s="157"/>
-      <c r="Z3" s="157"/>
-      <c r="AA3" s="101">
+      <c r="X3" s="190"/>
+      <c r="Y3" s="190"/>
+      <c r="Z3" s="190"/>
+      <c r="AA3" s="100">
         <v>0.08</v>
       </c>
-      <c r="AB3" s="101">
+      <c r="AB3" s="100">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="AC3" s="101">
+      <c r="AC3" s="100">
         <v>0.01</v>
       </c>
-      <c r="AD3" s="157"/>
-      <c r="AE3" s="157"/>
-      <c r="AF3" s="157"/>
-      <c r="AG3" s="157"/>
-      <c r="AH3" s="157"/>
+      <c r="AD3" s="190"/>
+      <c r="AE3" s="190"/>
+      <c r="AF3" s="190"/>
+      <c r="AG3" s="190"/>
+      <c r="AH3" s="190"/>
     </row>
     <row r="4" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81" t="s">
+      <c r="A4" s="79"/>
+      <c r="B4" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="80"/>
-      <c r="E4" s="82"/>
-      <c r="I4" s="104">
+      <c r="D4" s="79"/>
+      <c r="E4" s="81"/>
+      <c r="I4" s="103">
         <v>1</v>
       </c>
-      <c r="J4" s="105">
+      <c r="J4" s="104">
         <v>2</v>
       </c>
-      <c r="K4" s="105"/>
-      <c r="L4" s="104">
+      <c r="K4" s="104"/>
+      <c r="L4" s="103">
         <v>4</v>
       </c>
-      <c r="M4" s="104"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="107"/>
-      <c r="P4" s="107"/>
-      <c r="Q4" s="107"/>
-      <c r="R4" s="107"/>
-      <c r="S4" s="107">
+      <c r="M4" s="103"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="106">
         <v>11</v>
       </c>
-      <c r="T4" s="107">
+      <c r="T4" s="106">
         <v>12</v>
       </c>
-      <c r="U4" s="107">
+      <c r="U4" s="106">
         <v>13</v>
       </c>
-      <c r="V4" s="107">
+      <c r="V4" s="106">
         <v>14</v>
       </c>
-      <c r="W4" s="107">
+      <c r="W4" s="106">
         <v>15</v>
       </c>
-      <c r="X4" s="107">
+      <c r="X4" s="106">
         <v>16</v>
       </c>
-      <c r="Y4" s="107">
+      <c r="Y4" s="106">
         <v>17</v>
       </c>
-      <c r="Z4" s="107">
+      <c r="Z4" s="106">
         <v>18</v>
       </c>
-      <c r="AA4" s="107">
+      <c r="AA4" s="106">
         <v>19</v>
       </c>
-      <c r="AB4" s="107">
+      <c r="AB4" s="106">
         <v>20</v>
       </c>
-      <c r="AC4" s="107">
+      <c r="AC4" s="106">
         <v>21</v>
       </c>
-      <c r="AD4" s="107">
+      <c r="AD4" s="106">
         <v>22</v>
       </c>
-      <c r="AE4" s="107">
+      <c r="AE4" s="106">
         <v>23</v>
       </c>
-      <c r="AF4" s="108">
+      <c r="AF4" s="107">
         <v>24</v>
       </c>
-      <c r="AG4" s="107">
+      <c r="AG4" s="106">
         <v>25</v>
       </c>
-      <c r="AH4" s="107">
+      <c r="AH4" s="106">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A5" s="80"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="82"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="110">
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="81"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="109">
         <v>26</v>
       </c>
-      <c r="M5" s="111"/>
-      <c r="N5" s="112"/>
-      <c r="O5" s="111">
-        <v>0</v>
-      </c>
-      <c r="P5" s="111">
+      <c r="M5" s="110"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="110">
+        <v>0</v>
+      </c>
+      <c r="P5" s="110">
         <f>((M5/L5)*L5)+SUM(N5:O5)</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="111">
+      <c r="Q5" s="110">
         <f>P5-N5</f>
         <v>0</v>
       </c>
-      <c r="R5" s="111">
-        <v>0</v>
-      </c>
-      <c r="S5" s="111">
+      <c r="R5" s="110">
+        <v>0</v>
+      </c>
+      <c r="S5" s="110">
         <f>M5</f>
         <v>0</v>
       </c>
-      <c r="T5" s="103">
+      <c r="T5" s="102">
         <f>S5*T3</f>
         <v>0</v>
       </c>
-      <c r="U5" s="103">
+      <c r="U5" s="102">
         <f>S5*U3</f>
         <v>0</v>
       </c>
-      <c r="V5" s="103">
+      <c r="V5" s="102">
         <f>S5*V3</f>
         <v>0</v>
       </c>
-      <c r="W5" s="103">
-        <v>0</v>
-      </c>
-      <c r="X5" s="103">
+      <c r="W5" s="102">
+        <v>0</v>
+      </c>
+      <c r="X5" s="102">
         <f>SUM(T5:V5)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="103"/>
-      <c r="Z5" s="103">
+      <c r="Y5" s="102"/>
+      <c r="Z5" s="102">
         <v>15500000</v>
       </c>
-      <c r="AA5" s="103">
+      <c r="AA5" s="102">
         <f>S5*AA3</f>
         <v>0</v>
       </c>
-      <c r="AB5" s="103">
+      <c r="AB5" s="102">
         <f>S5*AB3</f>
         <v>0</v>
       </c>
-      <c r="AC5" s="103">
+      <c r="AC5" s="102">
         <f>S5*AC3</f>
         <v>0</v>
       </c>
-      <c r="AD5" s="103">
+      <c r="AD5" s="102">
         <f>SUM(AA5:AC5)</f>
         <v>0</v>
       </c>
-      <c r="AE5" s="103">
+      <c r="AE5" s="102">
         <f>MAX(Q5-Y5-Z5-AD5,0)</f>
         <v>0</v>
       </c>
-      <c r="AF5" s="103">
+      <c r="AF5" s="102">
         <f>MIN(AE5,10000000)*0.05+MAX(MIN(AE5-10000000,20000000),0)*0.1+MAX(MIN(AE5-30000000,30000000),0)*0.2+MAX(MIN(AE5-60000000,40000000),0)*0.3+MAX(AE5-100000000,0)*0.35</f>
         <v>0</v>
       </c>
-      <c r="AG5" s="103">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="103">
+      <c r="AG5" s="102">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="102">
         <f>P5+R5-AD5-AF5-AG5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:34" ht="25" x14ac:dyDescent="0.35">
-      <c r="A6" s="135" t="s">
+      <c r="A6" s="154" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="135"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="83"/>
-      <c r="R6" s="83"/>
-      <c r="S6" s="83"/>
-      <c r="T6" s="83"/>
-      <c r="U6" s="83"/>
-      <c r="V6" s="83"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="83"/>
-      <c r="Y6" s="83"/>
-      <c r="Z6" s="83"/>
-      <c r="AA6" s="83"/>
-      <c r="AB6" s="83"/>
-      <c r="AC6" s="83"/>
-      <c r="AD6" s="83"/>
-      <c r="AE6" s="83"/>
-      <c r="AF6" s="83"/>
-      <c r="AG6" s="83"/>
-      <c r="AH6" s="83"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="154"/>
+      <c r="D6" s="154"/>
+      <c r="E6" s="154"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="82"/>
+      <c r="L6" s="82"/>
+      <c r="M6" s="82"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="82"/>
+      <c r="Q6" s="82"/>
+      <c r="R6" s="82"/>
+      <c r="S6" s="82"/>
+      <c r="T6" s="82"/>
+      <c r="U6" s="82"/>
+      <c r="V6" s="82"/>
+      <c r="W6" s="82"/>
+      <c r="X6" s="82"/>
+      <c r="Y6" s="82"/>
+      <c r="Z6" s="82"/>
+      <c r="AA6" s="82"/>
+      <c r="AB6" s="82"/>
+      <c r="AC6" s="82"/>
+      <c r="AD6" s="82"/>
+      <c r="AE6" s="82"/>
+      <c r="AF6" s="82"/>
+      <c r="AG6" s="82"/>
+      <c r="AH6" s="82"/>
     </row>
     <row r="7" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="84" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="137"/>
-      <c r="D7" s="86" t="s">
+      <c r="B7" s="167"/>
+      <c r="C7" s="168"/>
+      <c r="D7" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="E7" s="87"/>
+      <c r="E7" s="86"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="134" t="s">
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="206" t="s">
         <v>114</v>
       </c>
-      <c r="M7" s="134"/>
-      <c r="N7" s="114">
+      <c r="M7" s="206"/>
+      <c r="N7" s="113">
         <f>AH5</f>
         <v>0</v>
       </c>
-      <c r="O7" s="114"/>
-      <c r="P7" s="113"/>
-      <c r="Q7" s="83"/>
-      <c r="R7" s="83"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="83"/>
-      <c r="W7" s="83"/>
-      <c r="X7" s="83"/>
-      <c r="Y7" s="83"/>
-      <c r="Z7" s="83"/>
-      <c r="AA7" s="83"/>
-      <c r="AB7" s="83"/>
-      <c r="AC7" s="83"/>
-      <c r="AD7" s="83"/>
-      <c r="AE7" s="83"/>
-      <c r="AF7" s="83"/>
-      <c r="AG7" s="83"/>
-      <c r="AH7" s="83"/>
+      <c r="O7" s="113"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="82"/>
+      <c r="R7" s="82"/>
+      <c r="S7" s="82"/>
+      <c r="T7" s="82"/>
+      <c r="U7" s="82"/>
+      <c r="V7" s="82"/>
+      <c r="W7" s="82"/>
+      <c r="X7" s="82"/>
+      <c r="Y7" s="82"/>
+      <c r="Z7" s="82"/>
+      <c r="AA7" s="82"/>
+      <c r="AB7" s="82"/>
+      <c r="AC7" s="82"/>
+      <c r="AD7" s="82"/>
+      <c r="AE7" s="82"/>
+      <c r="AF7" s="82"/>
+      <c r="AG7" s="82"/>
+      <c r="AH7" s="82"/>
     </row>
     <row r="8" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="85" t="s">
+      <c r="A8" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="138" t="s">
+      <c r="B8" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="139"/>
-      <c r="D8" s="139"/>
-      <c r="E8" s="140"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="170"/>
+      <c r="E8" s="171"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="134" t="s">
+      <c r="I8" s="82"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="82"/>
+      <c r="L8" s="206" t="s">
         <v>115</v>
       </c>
-      <c r="M8" s="134"/>
-      <c r="N8" s="114" t="e">
+      <c r="M8" s="206"/>
+      <c r="N8" s="113" t="e">
         <f>E26-N7</f>
         <v>#NUM!</v>
       </c>
-      <c r="O8" s="114"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="83"/>
-      <c r="U8" s="83"/>
-      <c r="V8" s="83"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="83"/>
-      <c r="Y8" s="83"/>
-      <c r="Z8" s="83"/>
-      <c r="AA8" s="83"/>
-      <c r="AB8" s="83"/>
-      <c r="AC8" s="83"/>
-      <c r="AD8" s="83"/>
-      <c r="AE8" s="83"/>
-      <c r="AF8" s="83"/>
-      <c r="AG8" s="83"/>
-      <c r="AH8" s="83"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="82"/>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="82"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="82"/>
+      <c r="U8" s="82"/>
+      <c r="V8" s="82"/>
+      <c r="W8" s="82"/>
+      <c r="X8" s="82"/>
+      <c r="Y8" s="82"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="82"/>
+      <c r="AB8" s="82"/>
+      <c r="AC8" s="82"/>
+      <c r="AD8" s="82"/>
+      <c r="AE8" s="82"/>
+      <c r="AF8" s="82"/>
+      <c r="AG8" s="82"/>
+      <c r="AH8" s="82"/>
     </row>
     <row r="9" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="89"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="89"/>
-      <c r="D9" s="89"/>
-      <c r="E9" s="90"/>
+      <c r="A9" s="88"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="89"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="91"/>
+      <c r="B10" s="156"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="157"/>
+      <c r="E10" s="90"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="115" t="s">
+      <c r="A11" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="91"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="90"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="115" t="s">
+      <c r="A12" s="155" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="92" t="e">
+      <c r="B12" s="156"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="157"/>
+      <c r="E12" s="91" t="e">
         <f>DAY(EOMONTH(DATE(E7,B7,1),0))</f>
         <v>#NUM!</v>
       </c>
@@ -6005,135 +6116,135 @@
       <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="155" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="91"/>
+      <c r="B13" s="156"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="157"/>
+      <c r="E13" s="90"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="115" t="s">
+      <c r="A14" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="116"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="91"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="157"/>
+      <c r="E14" s="90"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="115" t="s">
+      <c r="A15" s="155" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="91"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="157"/>
+      <c r="E15" s="90"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:34" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="115" t="s">
+      <c r="A16" s="155" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="116"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="91"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="157"/>
+      <c r="E16" s="90"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="115" t="s">
+      <c r="A17" s="155" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="116"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="93"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="92"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="115" t="s">
+      <c r="A18" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="116"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="94"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="93"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="121" t="s">
+      <c r="A19" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="121"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
+      <c r="B19" s="172"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="172"/>
+      <c r="E19" s="172"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="122" t="s">
+      <c r="A20" s="173" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="115" t="s">
+      <c r="B20" s="155" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="116"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="97"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="157"/>
+      <c r="E20" s="96"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="123"/>
-      <c r="B21" s="115" t="s">
+      <c r="A21" s="174"/>
+      <c r="B21" s="155" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="116"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="97"/>
+      <c r="C21" s="156"/>
+      <c r="D21" s="157"/>
+      <c r="E21" s="96"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="123"/>
-      <c r="B22" s="115" t="s">
+      <c r="A22" s="174"/>
+      <c r="B22" s="155" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="116"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="97"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="157"/>
+      <c r="E22" s="96"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="124"/>
-      <c r="B23" s="118" t="s">
+      <c r="A23" s="175"/>
+      <c r="B23" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="119"/>
-      <c r="D23" s="120"/>
-      <c r="E23" s="97" t="e">
+      <c r="C23" s="162"/>
+      <c r="D23" s="163"/>
+      <c r="E23" s="96" t="e">
         <f>((E20*(E12-E15))/E12)+E21*E13+E22</f>
         <v>#NUM!</v>
       </c>
@@ -6142,73 +6253,66 @@
       <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="125" t="s">
+      <c r="A24" s="158" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="126"/>
-      <c r="C24" s="126"/>
-      <c r="D24" s="126"/>
-      <c r="E24" s="127"/>
+      <c r="B24" s="159"/>
+      <c r="C24" s="159"/>
+      <c r="D24" s="159"/>
+      <c r="E24" s="160"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" s="6" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="118" t="s">
+      <c r="A25" s="161" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="119"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="120"/>
-      <c r="E25" s="97"/>
+      <c r="B25" s="162"/>
+      <c r="C25" s="162"/>
+      <c r="D25" s="163"/>
+      <c r="E25" s="96"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="70"/>
+      <c r="G25" s="69"/>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="128" t="s">
+      <c r="A26" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="129"/>
-      <c r="C26" s="129"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="98" t="e">
+      <c r="B26" s="165"/>
+      <c r="C26" s="165"/>
+      <c r="D26" s="166"/>
+      <c r="E26" s="97" t="e">
         <f>E23-E25</f>
         <v>#NUM!</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="76"/>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="78"/>
+      <c r="A35" s="75"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="77"/>
     </row>
     <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="76"/>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="79"/>
+      <c r="A36" s="75"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="S1:S3"/>
-    <mergeCell ref="T1:X1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AH1:AH3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="M1:M3"/>
-    <mergeCell ref="N1:N3"/>
-    <mergeCell ref="P1:P3"/>
-    <mergeCell ref="Q1:Q3"/>
-    <mergeCell ref="R1:R3"/>
-    <mergeCell ref="O1:O3"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="I1:I3"/>
     <mergeCell ref="J1:J3"/>
@@ -6225,17 +6329,24 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="M1:M3"/>
+    <mergeCell ref="N1:N3"/>
+    <mergeCell ref="P1:P3"/>
+    <mergeCell ref="Q1:Q3"/>
+    <mergeCell ref="R1:R3"/>
+    <mergeCell ref="O1:O3"/>
+    <mergeCell ref="S1:S3"/>
+    <mergeCell ref="T1:X1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AH1:AH3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/public/payslip-template.xlsx
+++ b/public/payslip-template.xlsx
@@ -3034,7 +3034,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A36" s="34"/>
       <c r="B36" s="30"/>
       <c r="C36" s="44"/>
@@ -3044,7 +3044,7 @@
       <c r="G36" s="11"/>
       <c r="H36" s="12"/>
     </row>
-    <row r="37" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A37" s="34"/>
       <c r="B37" s="30"/>
       <c r="C37" s="44"/>
@@ -3054,7 +3054,7 @@
       <c r="G37" s="11"/>
       <c r="H37" s="12"/>
     </row>
-    <row r="38" spans="1:8" ht="16.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A38" s="14"/>
       <c r="B38" s="15"/>
       <c r="C38" s="42"/>
